--- a/workspaces/btc_daily_14days/rsi/rsi_10.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_10.xlsx
@@ -575,46 +575,46 @@
         <v>50</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13.50656167979184</v>
+        <v>13.46660983015761</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.105531350499682</v>
+        <v>-2.09929834259065</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.502872272747368</v>
+        <v>5.486354797639137</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.637460378560782</v>
+        <v>9.609108835664365</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.100955871008352</v>
+        <v>9.073942091275001</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.400876985842416</v>
+        <v>9.373315936973569</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>15.32711449702126</v>
+        <v>15.2822044993927</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.845737011092581</v>
+        <v>4.831575448236258</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.230340183333865</v>
+        <v>-3.220115588466477</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.078745612406308</v>
+        <v>-2.071950091575744</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.294615184723668</v>
+        <v>-6.275159718376059</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.261361830836989</v>
+        <v>-6.242442530385318</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.684476413357963</v>
+        <v>-6.664273749700889</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.434027057166531</v>
+        <v>-6.414552417423693</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>68</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.271267562142299</v>
+        <v>9.242903853036097</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.132571717089817</v>
+        <v>9.105097325683204</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.6251862005157</v>
+        <v>14.58066751173708</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17.70257486398466</v>
+        <v>17.64905949704045</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.22402006951474</v>
+        <v>14.1807548707353</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.58042694947937</v>
+        <v>11.54547539964653</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.02566863047624</v>
+        <v>9.995415071821888</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.08697821997773</v>
+        <v>8.062621643570957</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.027386071847054</v>
+        <v>8.003962460413192</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.755567265633445</v>
+        <v>2.74798483143001</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.872216937344398</v>
+        <v>-1.865521720794533</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.586112234624338</v>
+        <v>2.578910094680396</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.6901061495021992</v>
+        <v>0.6886674267703725</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.940577161055657</v>
+        <v>0.938388759045317</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>81</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.34529017206183</v>
+        <v>-4.332819478871272</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2160653137833251</v>
+        <v>0.2149902021410526</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.825196901229198</v>
+        <v>-8.799225258404881</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.226005158799879</v>
+        <v>-6.207901959659367</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5872869465468398</v>
+        <v>-0.5866093106492798</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.418735315612096</v>
+        <v>3.407573534554167</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.09828572012718</v>
+        <v>2.091280189868847</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3939677027329793</v>
+        <v>0.3923630494454926</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3324518380096393</v>
+        <v>0.3318217341954792</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.469451369113429</v>
+        <v>-5.452002905184635</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.438927746945403</v>
+        <v>-4.424074983709836</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.119226708853738</v>
+        <v>-8.093747743494731</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.019816705038</v>
+        <v>-10.98526140402188</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.76931694870429</v>
+        <v>-10.73554007174559</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>90</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.395450568678662</v>
+        <v>6.374634392028419</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7718444140804621</v>
+        <v>-0.7698546432022297</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.503121752431667</v>
+        <v>5.485107399217249</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.634987729528163</v>
+        <v>5.616526782763238</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.20996633899756</v>
+        <v>6.189254488632237</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.509422062037096</v>
+        <v>6.488019496966928</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.200520790687612</v>
+        <v>4.186575983506451</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3940098138001673</v>
+        <v>0.3923329701117879</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.445921033520605</v>
+        <v>1.441753803105328</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5200698197298195</v>
+        <v>-0.5174346150609423</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3880070334782175</v>
+        <v>0.3883158379821552</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.920071755636933</v>
+        <v>-2.909832537221405</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.228231753608611</v>
+        <v>-2.219829305256447</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.8630733509035124</v>
+        <v>-0.8589968618690449</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.920788747560209</v>
+        <v>-2.935131419034278</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.823691670132256</v>
+        <v>-2.838841408910689</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.364220716546768</v>
+        <v>-2.375538308451382</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.089793551371166</v>
+        <v>-3.105110943111725</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.484997470627825</v>
+        <v>-4.50727164839504</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.044190408723516</v>
+        <v>-5.07002593499152</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.986588268578835</v>
+        <v>-6.01835313826934</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.600209378391092</v>
+        <v>-5.630807237162152</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.950234357958351</v>
+        <v>-3.97293208987832</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.517711074057253</v>
+        <v>-6.556192746963248</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.154228173990298</v>
+        <v>-4.180295025020747</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.835268983266623</v>
+        <v>-5.870312128684347</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5.767010392038685</v>
+        <v>-5.802204784183651</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.661651350801009</v>
+        <v>-4.690414486390118</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>131</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.46839374085873</v>
+        <v>2.459884936912026</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9.256378026855757</v>
+        <v>9.227653352022543</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.989946839784686</v>
+        <v>1.98291860299129</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1710664148844288</v>
+        <v>-0.1713883842833468</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.346937337072077</v>
+        <v>2.338473765579749</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3521369684782343</v>
+        <v>0.3501312462337012</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.267194503872318</v>
+        <v>0.2659057721132285</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9659934160076276</v>
+        <v>-0.9629404479155923</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.027855590563398</v>
+        <v>-1.0239985969693</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.006311223509464</v>
+        <v>4.992551561577599</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.333021882917549</v>
+        <v>6.315417118057624</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.837765607853306</v>
+        <v>4.82468315132035</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.181635512006011</v>
+        <v>5.167787319001228</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.666642757106366</v>
+        <v>4.654149872651736</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>148</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.196141022912677</v>
+        <v>-5.180635780523112</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.078482100183948</v>
+        <v>-2.073012965779292</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.502303827201601</v>
+        <v>-4.488976296330947</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.373227265793695</v>
+        <v>-4.360028150814991</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.8544183994748238</v>
+        <v>-0.853253138418566</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.940234978957335</v>
+        <v>-3.928566464708524</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.318991005169408</v>
+        <v>-1.315271388617077</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.819127650806543</v>
+        <v>-3.806626776888208</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.17284414118771</v>
+        <v>-1.168204329519497</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.703428485910777</v>
+        <v>-2.693457728404191</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.909800069909153</v>
+        <v>-2.899046302503983</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.554219275047913</v>
+        <v>-3.541316436053137</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.653975339022466</v>
+        <v>-4.637246722673709</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.758973618539464</v>
+        <v>-5.738876741748925</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>163</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2672978761090405</v>
+        <v>0.2657899767608285</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.723834443041333</v>
+        <v>1.716953752522564</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.557024484084074</v>
+        <v>2.547727284477098</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.460035225153952</v>
+        <v>1.454748355940524</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.150401087731403</v>
+        <v>2.141504601120403</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.238026698529502</v>
+        <v>-1.234390004272498</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.937970478415764</v>
+        <v>-1.931799161354419</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.5629981239917328</v>
+        <v>-0.5603247825466937</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.009633103190772374</v>
+        <v>-0.008487394320013664</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2475639443580988</v>
+        <v>-0.2449534836725604</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.761069875505164</v>
+        <v>-4.743018973744022</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.034903594751206</v>
+        <v>-1.029295212375757</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8414749807590027</v>
+        <v>-0.8360528908050426</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.206435743969529</v>
+        <v>-1.199828491044229</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.46962879640045</v>
+        <v>-5.483976254161057</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.848102071048103</v>
+        <v>1.854251805358615</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.644905554269961</v>
+        <v>2.65299717315677</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.371926135621123</v>
+        <v>3.381597243344359</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.238505444638996</v>
+        <v>2.246259233034664</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.13275093523221</v>
+        <v>3.141580560143865</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.837936747195485</v>
+        <v>4.851174554555193</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.580830099024617</v>
+        <v>2.587132515505267</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.520217599061723</v>
+        <v>2.526138447085138</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.05560346703875</v>
+        <v>4.065115744154539</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.641951819523321</v>
+        <v>5.65503247067246</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9.002847044189281</v>
+        <v>9.025441939088324</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.778454673872609</v>
+        <v>9.802792118562586</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>6.44444699823994</v>
+        <v>6.459699079581384</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>157</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.920574418643525</v>
+        <v>2.910883304835387</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.309631180009461</v>
+        <v>1.303327436706574</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.552471018504491</v>
+        <v>1.545489797191351</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.045841491232501</v>
+        <v>1.040987292758153</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.319186951763328</v>
+        <v>-3.310449658198721</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.29899623111568</v>
+        <v>-4.285274662764891</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.385274988874862</v>
+        <v>-4.371265281104094</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-6.132955280457821</v>
+        <v>-6.11150189882143</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.473893105931467</v>
+        <v>-7.447555660783749</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-6.413003346940727</v>
+        <v>-6.389799971854757</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-10.45625985689048</v>
+        <v>-10.4185296846366</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.97716140562397</v>
+        <v>-12.93191722792796</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-8.925304607559852</v>
+        <v>-8.893573112758361</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.840588921591717</v>
+        <v>-4.822195729526371</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>178</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.369842814591998</v>
+        <v>-1.365091958550593</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.230281775880314</v>
+        <v>-5.21353840499809</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5672736682870365</v>
+        <v>-0.5673871773907209</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.250207206941397</v>
+        <v>1.244016586891817</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.101207052506858</v>
+        <v>-2.095839316716152</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.804774235356739</v>
+        <v>-1.798461805593163</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.016387527785454</v>
+        <v>-3.005653720418266</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.234301587328396</v>
+        <v>-1.228070221017525</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.98690109259698</v>
+        <v>-2.973690696250543</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-6.096040805689618</v>
+        <v>-6.071160990238774</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.794811306115285</v>
+        <v>-1.784020273629373</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.270359010398003</v>
+        <v>-6.244019138755988</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.74478472280407</v>
+        <v>-2.731689480037971</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.74946439552091</v>
+        <v>-4.729159158997767</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>192</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4101049868766395</v>
+        <v>-0.4084236537570973</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.9802647697600335</v>
+        <v>-0.9777364039029663</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.502936609135915</v>
+        <v>-4.487656762311182</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8403506351724914</v>
+        <v>0.8348679384977515</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.344890308956913</v>
+        <v>1.337542730975962</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.729948491381855</v>
+        <v>3.715504606245382</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.690391401862115</v>
+        <v>4.672504895771823</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.611114268478431</v>
+        <v>1.607107360308781</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.116829156153223</v>
+        <v>3.108054644183355</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1728059610904964</v>
+        <v>0.1767449245634012</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.03386176500445259</v>
+        <v>-0.02840229610141876</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5225029120649509</v>
+        <v>-0.5148524720893235</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.194238941552982</v>
+        <v>2.189892916965661</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6927488502651116</v>
+        <v>-0.6853857507579377</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.763708590480242</v>
+        <v>-2.784865842129669</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.458546725310541</v>
+        <v>-5.497419130107318</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.478977943250648</v>
+        <v>-4.510330105244499</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.598700333203318</v>
+        <v>-7.650806317420162</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-10.84398159210516</v>
+        <v>-10.92041940918524</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.298190920002</v>
+        <v>-4.32871612970149</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.632458515322028</v>
+        <v>-7.688154560996949</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.008953566414462</v>
+        <v>-7.065465417889506</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-11.40630288465839</v>
+        <v>-11.49733821840616</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.913407699651472</v>
+        <v>-7.982305058231461</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-7.57657185450195</v>
+        <v>-7.644522514680652</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.829741767716634</v>
+        <v>-4.877898920176754</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.708797079580656</v>
+        <v>-4.751705443689836</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.085605660017571</v>
+        <v>-6.141328373708753</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.766165592937149</v>
+        <v>-4.798188154216149</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.858543874206148</v>
+        <v>-3.88382132698753</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.747931092415925</v>
+        <v>0.7525665936284724</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.851131857547365</v>
+        <v>-1.862112328861087</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.707197841955974</v>
+        <v>1.717277413336063</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.91335415296971</v>
+        <v>2.931359499371567</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.362175840713192</v>
+        <v>-5.398534196459011</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.096419492752631</v>
+        <v>-3.123082490061535</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.524821664169465</v>
+        <v>-4.564094312268708</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.552505075652348</v>
+        <v>-3.587612414364656</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7552115006967242</v>
+        <v>-0.7738151401381188</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7216309543542465</v>
+        <v>-0.7394319827925813</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.054859444254809</v>
+        <v>-2.077117786398034</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.715436620924329</v>
+        <v>-2.744827646782298</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>193</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.306909822800769</v>
+        <v>-4.291283850014004</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.7371362855059616</v>
+        <v>-0.7332645528508266</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.09573556205049982</v>
+        <v>-0.09561353036232134</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.075890403496452</v>
+        <v>-3.066292300108366</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.060372800549501</v>
+        <v>-2.054177767680002</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.318449273991092</v>
+        <v>-3.308911442883002</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-6.001328186139212</v>
+        <v>-5.980026392574423</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.839848769990489</v>
+        <v>-2.826452139440057</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.905186974932803</v>
+        <v>-2.889263687980737</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.241630147158723</v>
+        <v>-3.223908039141357</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.927085236303476</v>
+        <v>-2.910526648433027</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.931729289818477</v>
+        <v>-3.91241292113952</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.831824184561015</v>
+        <v>-3.814532817058527</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.05499491632689768</v>
+        <v>0.06213152039911307</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.178878063970821</v>
+        <v>1.178561371301562</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.517441311705241</v>
+        <v>-5.53504991894539</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.782366515477165</v>
+        <v>-4.795872962986529</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.65493337368865</v>
+        <v>-4.669257645235163</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.06533962923875</v>
+        <v>-4.077399826696201</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.161140232636612</v>
+        <v>-7.181866217535323</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.060336617531071</v>
+        <v>-8.088000298413036</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-9.09573607913179</v>
+        <v>-9.12729868374003</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.063689121780001</v>
+        <v>-4.083281184879198</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.480949459244158</v>
+        <v>-5.505467153602147</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.152897822040515</v>
+        <v>-1.164765932464924</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.38491714545556</v>
+        <v>-3.403110047846894</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.805755787558027</v>
+        <v>-3.823364658791796</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.689162691767365</v>
+        <v>-4.710006962879142</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.652903143204661</v>
+        <v>1.655694206197808</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9342802258572647</v>
+        <v>-0.9517004585886397</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8413440544049635</v>
+        <v>-0.8513323211132047</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.200205313176298</v>
+        <v>-1.216545201181283</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.444180098941317</v>
+        <v>-2.468144092119161</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.587552016853323</v>
+        <v>-4.630419365303958</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.711941763417492</v>
+        <v>-2.753990351174409</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.667554252094369</v>
+        <v>-3.720872419438038</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.24265917632399</v>
+        <v>-3.295958394401879</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.351736035172138</v>
+        <v>-1.393846016118815</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.025358676856499</v>
+        <v>-3.076431852751774</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.989645454763526</v>
+        <v>-3.04204869540623</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.877882673243398</v>
+        <v>-4.940135818666405</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.093483819006998</v>
+        <v>-6.168246998705385</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>168</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-5.46962879640045</v>
+        <v>-5.455280427624764</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.656892828730598</v>
+        <v>0.6587971224158409</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.880833020723209</v>
+        <v>-6.864907961328676</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.373541419197629</v>
+        <v>-4.361799683094837</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.912234119497533</v>
+        <v>-4.899677927711274</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.21063492417921</v>
+        <v>-5.196264790915556</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.105357315561832</v>
+        <v>-4.089592588538594</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.195052087681979</v>
+        <v>-2.18197409273364</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.454475583303008</v>
+        <v>-3.43780950104162</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.114028977363468</v>
+        <v>-3.097458495593365</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.721863096108329</v>
+        <v>-2.706973724672849</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.284399144335616</v>
+        <v>-3.267828662565513</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.511495890005513</v>
+        <v>-2.497607083034225</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.455476859700624</v>
+        <v>-3.438361941234128</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.182879313998797</v>
+        <v>-2.202531806530821</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.036688951807839</v>
+        <v>-5.067699811287063</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.325967596292564</v>
+        <v>-2.343577261249635</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.01643822966835984</v>
+        <v>0.008234474571523265</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.382684561407935</v>
+        <v>-2.401488674214328</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.022557822805439</v>
+        <v>1.016504864924983</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.434232230906112</v>
+        <v>3.430842164817371</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.728464400312681</v>
+        <v>1.71485074559115</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.668256122128241</v>
+        <v>1.651476213244088</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.68974290358134</v>
+        <v>2.67635102821616</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.004794955207636065</v>
+        <v>-0.02840229610141876</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.275137941008452</v>
+        <v>1.255980861244005</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2317797248107212</v>
+        <v>0.2107262502991105</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.594389196811299</v>
+        <v>3.585447582575398</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>149</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.157867850411314</v>
+        <v>-2.149172903081734</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.084877704986312</v>
+        <v>-1.078296734555877</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.150887351180216</v>
+        <v>-2.143374814382355</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6783523393780868</v>
+        <v>-0.6734357937560276</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.887914494047493</v>
+        <v>-1.880454093487728</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.107514020849301</v>
+        <v>3.106401453202572</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.365062182771652</v>
+        <v>4.36487134446616</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.568583687431072</v>
+        <v>4.569455759743924</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.833366843520558</v>
+        <v>3.83687889780785</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.9642260067629564</v>
+        <v>0.9733308939879706</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7594726824453772</v>
+        <v>0.7685775696703914</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.24064564182121</v>
+        <v>-3.223884910568067</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.660606100945522</v>
+        <v>-3.644139521512969</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.7217073672954513</v>
+        <v>-0.7098544308474217</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>168</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.1052289935646797</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.295488123650287</v>
+        <v>-5.277584536340676</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-9.857023496913676</v>
+        <v>-9.830336664365362</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.355076160573844</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.312810626997468</v>
+        <v>-4.297575722942717</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.396321070234052</v>
+        <v>-6.377331282020727</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.290578597030205</v>
+        <v>-5.270025054067588</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.557127764787865</v>
+        <v>-7.529824798264258</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7.037378156076819</v>
+        <v>-7.009238072470197</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-4.311519897711655</v>
+        <v>-4.287934686069484</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-6.305844342054051</v>
+        <v>-6.278402296101483</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.273040583036781</v>
+        <v>-6.244019138755924</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.517234397675416</v>
+        <v>-2.497607083034161</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.670594509142155</v>
+        <v>-1.652647655519772</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>144</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.10454943132109</v>
+        <v>-1.091873743229712</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.021678599840975</v>
+        <v>-2.005001670448529</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.805436195326379</v>
+        <v>-3.783566815390557</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.147405284941101</v>
+        <v>-7.119976928541107</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.130270944457713</v>
+        <v>-2.114540873693748</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.916162340075466</v>
+        <v>-3.89594232678283</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.223118279569889</v>
+        <v>-1.204761439707511</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.3840765256906025</v>
+        <v>0.4019867842734115</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.488763168906509</v>
+        <v>4.498698435466274</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.547214504917982</v>
+        <v>1.56523991710489</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.126514671155121</v>
+        <v>4.138264370565409</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.551129320978475</v>
+        <v>5.561536416799491</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.525801479063418</v>
+        <v>6.530170694743475</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.383910355169931</v>
+        <v>5.391003138130877</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.548519721748065</v>
+        <v>5.552741029119787</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>10.2306524024901</v>
+        <v>10.25535071070775</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>12.63298649309631</v>
+        <v>12.66740600857928</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.966036828501011</v>
+        <v>9.990037278968266</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12.92411910993235</v>
+        <v>12.96655178923535</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>11.1236589497459</v>
+        <v>11.15461357709718</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>13.13682733037573</v>
+        <v>13.16879214342175</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>12.41689540298363</v>
+        <v>12.43726173782188</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.96345699141735</v>
+        <v>10.97365931183568</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.421984311173645</v>
+        <v>9.419308774695111</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.61732186464829</v>
+        <v>10.62300615460273</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.854306608386878</v>
+        <v>7.840487903497532</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.62482438042985</v>
+        <v>4.603331884101927</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.873849877211711</v>
+        <v>4.853053216378214</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>10.31647903516188</v>
+        <v>10.36407598036202</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>12.83713682715635</v>
+        <v>12.90486846204157</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.61582183956803</v>
+        <v>11.67146621410335</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.09318241019211</v>
+        <v>10.13895283605043</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.901868633136409</v>
+        <v>7.939065162319949</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.54641800886855</v>
+        <v>6.565940277362593</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.941023134571523</v>
+        <v>8.965605936065415</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.473839735790023</v>
+        <v>8.478921757252721</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>11.42032951902923</v>
+        <v>11.44314287991075</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.761836565406284</v>
+        <v>9.759684361549532</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.900316712163047</v>
+        <v>7.888264370565253</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.12116681165724</v>
+        <v>7.089314194577341</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.865426663522243</v>
+        <v>5.835726250299111</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.113856673484499</v>
+        <v>6.085447582575398</v>
       </c>
     </row>
     <row r="30">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 14.35</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4085~4097</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4085</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.0328003910421657</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 17.07</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4035~4047</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4035</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.1336656490955761</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 19.78</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3967~3979</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3967</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2943933340325415</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 22.5</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3886~3898</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3886</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2102161549970489</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 25.22</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3796~3808</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3796</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.3663374798738346</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 27.94</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3680~3691</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3680</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2853646274437835</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 30.65</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3549~3560</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3549</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.3866967471762663</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 33.37</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3401~3412</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3401</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.178080758662496</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 36.09</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3238~3249</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3238</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.2004250853684866</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 38.81</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3071~3081</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3071</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.08689274113374523</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 41.53</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2914~2924</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2914</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.06525774565456999</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 44.24</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2736~2746</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2736</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.01930749188033332</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 46.96</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2544~2554</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2544</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.0515890877774936</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 49.68</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2361~2369</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2361</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.2714413758643204</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 52.4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2143~2149</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2143</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.7871573056625181</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 55.12</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1950~1956</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1950</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.289792763634608</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 57.83</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1774~1779</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1774</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.300828121611275</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 60.55</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1571~1574</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1571</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.254973369751909</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 63.27</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1403~1406</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1403</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.058482021184048</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 65.99</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1243~1245</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1243</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.606963286215723</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 68.71</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1094~1096</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1094</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.254736862271777</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 71.42</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>926~928</t>
-        </is>
+      <c r="B27" t="n">
+        <v>926</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>3.864320300479683</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 74.14</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>782~784</t>
-        </is>
+      <c r="B28" t="n">
+        <v>782</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>4.776969843055333</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 76.86</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>640~641</t>
-        </is>
+      <c r="B29" t="n">
+        <v>640</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>4.604845611147276</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 79.58</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>520~520</t>
-        </is>
+      <c r="B30" t="n">
+        <v>520</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>3.275792449020798</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 82.3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>395~395</t>
-        </is>
+      <c r="B31" t="n">
+        <v>395</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.936941426625467</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 85.01</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>293~293</t>
-        </is>
+      <c r="B32" t="n">
+        <v>293</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.796664068868523</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 87.73</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>210~210</t>
-        </is>
+      <c r="B33" t="n">
+        <v>210</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>4.173228346456689</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 90.45</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>150~150</t>
-        </is>
+      <c r="B34" t="n">
+        <v>150</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.173228346456689</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 93.17</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>5.83989501312336</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 14.35</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-1.302962129733785</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 17.07</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>133~134</t>
-        </is>
+      <c r="B7" t="n">
+        <v>133</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>4.222979590237784</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 19.78</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>201~202</t>
-        </is>
+      <c r="B8" t="n">
+        <v>201</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>5.922403263948439</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 22.5</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>282~283</t>
-        </is>
+      <c r="B9" t="n">
+        <v>282</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>2.983593481910162</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 25.22</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>372~373</t>
-        </is>
+      <c r="B10" t="n">
+        <v>372</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3.806829776304774</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 27.94</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>488~490</t>
-        </is>
+      <c r="B11" t="n">
+        <v>488</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>2.200439230810431</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 30.65</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>619~621</t>
-        </is>
+      <c r="B12" t="n">
+        <v>619</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2.256964256279559</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 33.37</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>767~769</t>
-        </is>
+      <c r="B13" t="n">
+        <v>767</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.8225564782295578</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 36.09</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>930~932</t>
-        </is>
+      <c r="B14" t="n">
+        <v>930</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.7254457999616974</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 38.81</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1097~1100</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1097</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.2207110474827019</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 41.53</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1254~1257</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1254</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.1716372565601176</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 44.24</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1432~1435</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1432</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.01957072439116558</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 46.96</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1624~1627</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1624</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.0656571278313649</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 49.68</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1807~1812</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1807</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.3411204394152705</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 52.4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2025~2032</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2025</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.8202099737532862</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 55.12</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2218~2225</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2218</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.12265180335605</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 57.83</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2394~2402</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2394</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.9530553060551057</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 60.55</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2597~2607</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2597</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.7481372078202568</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 63.27</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2765~2775</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2765</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.033978860750523</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 65.99</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2925~2936</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2925</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.096980554542398</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 68.71</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3074~3085</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3074</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.148219519561678</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 71.42</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3242~3253</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3242</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.094729436102995</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 74.14</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3386~3397</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3386</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.095145709082516</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 76.86</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3528~3540</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3528</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.8267716535433038</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 79.58</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3648~3661</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3648</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.4584751953806929</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 82.3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3773~3786</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3773</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.1954985420800242</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 85.01</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3875~3888</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3875</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.2043436700042136</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 87.73</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3958~3971</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3958</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.2144154040679496</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 90.45</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4018~4031</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4018</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.07468366875872334</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 93.17</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4084~4097</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4084</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.1136482298999866</v>

--- a/workspaces/btc_daily_14days/rsi/rsi_10.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_10.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-10 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-10 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>50</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13.46660983015761</v>
+        <v>13.47577232800231</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.09929834259065</v>
+        <v>-2.08590981126514</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.486354797639137</v>
+        <v>5.497953085427561</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.609108835664365</v>
+        <v>9.619698321100024</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.073942091275001</v>
+        <v>9.084776914150716</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.373315936973569</v>
+        <v>9.384040171577055</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>15.2822044993927</v>
+        <v>15.2915115103586</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.831575448236258</v>
+        <v>4.843558033616084</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.220115588466477</v>
+        <v>-3.206082630895175</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.071950091575744</v>
+        <v>-2.057992863822591</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.275159718376059</v>
+        <v>-6.260092616689022</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.242442530385318</v>
+        <v>-6.227421246598283</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.649038009045604</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.414552417423693</v>
+        <v>-6.424982053121845</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>68</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.242903853036097</v>
+        <v>9.253027971620007</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.105097325683204</v>
+        <v>9.115684171535655</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.58066751173708</v>
+        <v>14.58993785677497</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17.64905949704045</v>
+        <v>17.65755646797131</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.1807548707353</v>
+        <v>14.19023773722163</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.54547539964653</v>
+        <v>11.55558434832821</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.995415071821888</v>
+        <v>10.005940804156</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.062621643570957</v>
+        <v>8.073755384193305</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.003962460413192</v>
+        <v>8.015194400803445</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.74798483143001</v>
+        <v>2.760744681416703</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.865521720794533</v>
+        <v>-1.851517510959212</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.578910094680396</v>
+        <v>2.591755462314516</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.6886674267703725</v>
+        <v>0.7021000582379742</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.938388759045317</v>
+        <v>0.9279591233471649</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>81</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.332819478871272</v>
+        <v>-4.31930515873897</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2149902021410526</v>
+        <v>0.2277689375599579</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.799225258404881</v>
+        <v>-8.784098328403545</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.207901959659367</v>
+        <v>-6.193452956411001</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5866093106492798</v>
+        <v>-0.5734738635619934</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.407573534554167</v>
+        <v>3.419660075343998</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.091280189868847</v>
+        <v>2.103739032170495</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3923630494454926</v>
+        <v>0.4053891887219621</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3318217341954792</v>
+        <v>0.344950124787168</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.452002905184635</v>
+        <v>-5.437159805490126</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.424074983709836</v>
+        <v>-4.409391924875031</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.093747743494731</v>
+        <v>-8.078180609760516</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-10.98526140402188</v>
+        <v>-10.96883017723178</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.73554007174559</v>
+        <v>-10.74596970744374</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>90</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.374634392028419</v>
+        <v>6.385382154885455</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7698546432022297</v>
+        <v>-0.7568231685069122</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.485107399217249</v>
+        <v>5.496577421652326</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.616526782763238</v>
+        <v>5.627935039154757</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.189254488632237</v>
+        <v>6.200610264262153</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.488019496966928</v>
+        <v>6.499253255749927</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.186575983506451</v>
+        <v>4.198456555168519</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3923329701117879</v>
+        <v>0.4053521518157197</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.441753803105328</v>
+        <v>1.454587018313134</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5174346150609423</v>
+        <v>-0.5038253772267183</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3883158379821552</v>
+        <v>0.4017873187759236</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.909832537221405</v>
+        <v>-2.895535091930192</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.219829305256447</v>
+        <v>-2.20557710829064</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>116</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.935131419034278</v>
+        <v>-2.921840244305997</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.838841408910689</v>
+        <v>-2.825116884730079</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.375538308451382</v>
+        <v>-2.361898113331357</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.105110943111725</v>
+        <v>-3.091300727858588</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.50727164839504</v>
+        <v>-4.492987183381324</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.07002593499152</v>
+        <v>-5.0556325517475</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.01835313826934</v>
+        <v>-6.003643672515182</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.630807237162152</v>
+        <v>-5.616034152207149</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.97293208987832</v>
+        <v>-3.958520357990736</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.556192746963248</v>
+        <v>-6.540800509793613</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.180295025020747</v>
+        <v>-4.16544914732097</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.870312128684347</v>
+        <v>-5.85503029551284</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5.802204784183651</v>
+        <v>-6.281324443698047</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.690414486390118</v>
+        <v>-4.70084412208827</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>131</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.459884936912026</v>
+        <v>2.471588653168311</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9.227653352022543</v>
+        <v>9.237914636186531</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.98291860299129</v>
+        <v>1.9952473164496</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1713883842833468</v>
+        <v>-0.1584755297615885</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.338473765579749</v>
+        <v>2.350783638943611</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3501312462337012</v>
+        <v>0.3629631648186944</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2659057721132285</v>
+        <v>0.2788300911759762</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9629404479155923</v>
+        <v>-0.9495033549943983</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.0239985969693</v>
+        <v>-1.010466560328339</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.992551561577599</v>
+        <v>5.004693881554026</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.315417118057624</v>
+        <v>6.327266174096174</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.82468315132035</v>
+        <v>4.836942110523403</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.167787319001228</v>
+        <v>5.181343365352831</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.654149872651736</v>
+        <v>4.643720236953584</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>148</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.180635780523112</v>
+        <v>-5.166760327163281</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.073012965779292</v>
+        <v>-2.059656216278881</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.488976296330947</v>
+        <v>-4.47480571354123</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.360028150814991</v>
+        <v>-4.345892379739212</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.853253138418566</v>
+        <v>-0.84007255013735</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.928566464708524</v>
+        <v>-3.91449633164811</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.315271388617077</v>
+        <v>-1.301894596050488</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.806626776888208</v>
+        <v>-3.792333802093559</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.168204329519497</v>
+        <v>-1.154602631854878</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.693457728404191</v>
+        <v>-2.679160976598524</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.899046302503983</v>
+        <v>-2.88462135310445</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.541316436053137</v>
+        <v>-3.526696200938048</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.637246722673709</v>
+        <v>-4.623690676322106</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.738876741748925</v>
+        <v>-5.749306377447077</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>163</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2657899767608285</v>
+        <v>0.2781190941667191</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.716953752522564</v>
+        <v>1.729186781369897</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.547727284477098</v>
+        <v>2.559842796391059</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.454748355940524</v>
+        <v>1.467204094682529</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.141504601120403</v>
+        <v>2.153769275986761</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.234390004272498</v>
+        <v>-1.221051675781069</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.931799161354419</v>
+        <v>-1.918202545984535</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.5603247825466937</v>
+        <v>-0.5469261897208426</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.008487394320013664</v>
+        <v>0.004795242032415103</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2449534836725604</v>
+        <v>-0.2313266513772163</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.743018973744022</v>
+        <v>-4.727932013976314</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.029295212375757</v>
+        <v>-1.015338388775085</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8360528908050426</v>
+        <v>-0.8224968444534397</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.199828491044229</v>
+        <v>-1.210258126742382</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>167</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.483976254161057</v>
+        <v>-5.469701062178473</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.854251805358615</v>
+        <v>1.866471566887718</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.65299717315677</v>
+        <v>2.665087683459198</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.381597243344359</v>
+        <v>3.393476007334066</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.246259233034664</v>
+        <v>2.258504258259201</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.141580560143865</v>
+        <v>3.153634346710163</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.851174554555193</v>
+        <v>4.862729344550822</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.587132515505267</v>
+        <v>2.59963873753113</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.526138447085138</v>
+        <v>2.538713693639146</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.065115744154539</v>
+        <v>4.077474153941921</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.65503247067246</v>
+        <v>5.667021504410116</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9.025441939088324</v>
+        <v>8.697989128467022</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.802792118562586</v>
+        <v>9.816348164914189</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>6.459699079581384</v>
+        <v>6.449269443883232</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>157</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.910883304835387</v>
+        <v>2.589694345943684</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.303327436706574</v>
+        <v>1.315549562440566</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.545489797191351</v>
+        <v>1.55774696201113</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.040987292758153</v>
+        <v>1.053434330913163</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.310449658198721</v>
+        <v>-3.296509372945053</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.285274662764891</v>
+        <v>-4.270898706106856</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.371265281104094</v>
+        <v>-4.356830752824955</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-6.11150189882143</v>
+        <v>-6.096203145472707</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.447555660783749</v>
+        <v>-7.431744437881733</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-6.389799971854757</v>
+        <v>-6.374088696325295</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-10.4185296846366</v>
+        <v>-10.40130701703636</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.93191722792796</v>
+        <v>-12.91846493920785</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-8.893573112758361</v>
+        <v>-8.880017066406758</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.822195729526371</v>
+        <v>-4.832625365224523</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>178</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.365091958550593</v>
+        <v>-1.35256966887497</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.21353840499809</v>
+        <v>-5.199026952332567</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5673871773907209</v>
+        <v>-0.5544518201614395</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.244016586891817</v>
+        <v>1.256324673073152</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.095839316716152</v>
+        <v>-2.082240531370651</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.798461805593163</v>
+        <v>-1.784829918094857</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.005653720418266</v>
+        <v>-2.991550180748249</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.228070221017525</v>
+        <v>-1.214294820741266</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.973690696250543</v>
+        <v>-2.959193340760962</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-6.071160990238774</v>
+        <v>-6.055283929261279</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.784020273629373</v>
+        <v>-1.76949147126826</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.731689480037971</v>
+        <v>-2.718133433686369</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.729159158997767</v>
+        <v>-4.739588794695919</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>192</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4084236537570973</v>
+        <v>-0.3959013640814746</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.9777364039029663</v>
+        <v>-0.9646514171960447</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.487656762311182</v>
+        <v>-4.473196253050851</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8348679384977515</v>
+        <v>0.8472390567509365</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.337542730975962</v>
+        <v>1.349866397117907</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.715504606245382</v>
+        <v>3.727059615442784</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.672504895771823</v>
+        <v>4.683746778702115</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.607107360308781</v>
+        <v>1.619856366189879</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.108054644183355</v>
+        <v>3.12035284096762</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1767449245634012</v>
+        <v>0.1905272131197506</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.02840229610141876</v>
+        <v>-0.01440754473273387</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5148524720893235</v>
+        <v>-0.5014001833692134</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.189892916965661</v>
+        <v>2.203448963317264</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6853857507579377</v>
+        <v>-0.6958153864560899</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>183</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.784865842129669</v>
+        <v>-2.772343552454046</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.497419130107318</v>
+        <v>-5.482151109337266</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.510330105244499</v>
+        <v>-4.79241448232812</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.650806317420162</v>
+        <v>-7.634824724484389</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-10.92041940918524</v>
+        <v>-10.90291722481253</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.32871612970149</v>
+        <v>-4.612101238716967</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.688154560996949</v>
+        <v>-7.671977546962083</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.065465417889506</v>
+        <v>-7.049117861692132</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-11.49733821840616</v>
+        <v>-11.47900461995159</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.982305058231461</v>
+        <v>-7.965010080161136</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-7.644522514680652</v>
+        <v>-7.627217997503323</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.877898920176754</v>
+        <v>-4.864446631456644</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.751705443689836</v>
+        <v>-4.738149397338233</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.141328373708753</v>
+        <v>-6.151758009406905</v>
       </c>
     </row>
     <row r="19">
@@ -1251,98 +1251,98 @@
         <v>218</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.798188154216149</v>
+        <v>-4.785665864540526</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.88382132698753</v>
+        <v>-4.118800804473921</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7525665936284724</v>
+        <v>0.7655737250460746</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.862112328861087</v>
+        <v>-1.848283438113448</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.717277413336063</v>
+        <v>1.729697601838112</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.931359499371567</v>
+        <v>2.944402395665932</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.398534196459011</v>
+        <v>-5.382723783542104</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.123082490061535</v>
+        <v>-3.107858788259499</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.564094312268708</v>
+        <v>-4.547909179312398</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.587612414364656</v>
+        <v>-3.571513770767751</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7738151401381188</v>
+        <v>-1.028362724893498</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7394319827925813</v>
+        <v>-0.7259796940724712</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.077117786398034</v>
+        <v>-2.063561740046431</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.744827646782298</v>
+        <v>-2.75525728248045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 53.76</t>
+          <t>X ≈ 53.75</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.291283850014004</v>
+        <v>-4.547804001703604</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.7332645528508266</v>
+        <v>-0.962487732714564</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.09561353036232134</v>
+        <v>0.1998797182427765</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.066292300108366</v>
+        <v>-2.78545681401333</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.054177767680002</v>
+        <v>-1.765549591629444</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.308911442883002</v>
+        <v>-3.029255212109362</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.980026392574423</v>
+        <v>-5.710326286638363</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.826452139440057</v>
+        <v>-2.538943788411274</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.889263687980737</v>
+        <v>-2.601162630170997</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.223908039141357</v>
+        <v>-2.932448203991477</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.910526648433027</v>
+        <v>-2.619111669057986</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.91241292113952</v>
+        <v>-4.147233516702784</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.814532817058527</v>
+        <v>-3.525717703349407</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.06213152039911307</v>
+        <v>-0.174982053122875</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.178561371301562</v>
+        <v>1.452023228891342</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.53504991894539</v>
+        <v>-5.232358644179875</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.795872962986529</v>
+        <v>-5.062736312175559</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.669257645235163</v>
+        <v>-4.933232494817545</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.077399826696201</v>
+        <v>-4.34820827112835</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.181866217535323</v>
+        <v>-7.436149905678057</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.088000298413036</v>
+        <v>-8.655162658181254</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-9.12729868374003</v>
+        <v>-9.367554396318546</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.083281184879198</v>
+        <v>-4.354855425245667</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.505467153602147</v>
+        <v>-5.772779733730083</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.164765932464924</v>
+        <v>-1.462685115385291</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.403110047846894</v>
+        <v>-3.123222217267383</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.823364658791796</v>
+        <v>-4.108344821993349</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.710006962879142</v>
+        <v>-4.447580923179252</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>203</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.655694206197808</v>
+        <v>1.66821649587343</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9517004585886397</v>
+        <v>-0.9387906490125886</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8513323211132047</v>
+        <v>-0.8383251896956025</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.216545201181283</v>
+        <v>-1.202000049259553</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.468144092119161</v>
+        <v>-2.72775223268593</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.630419365303958</v>
+        <v>-4.617376469009592</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.753990351174409</v>
+        <v>-2.740924096873933</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.720872419438038</v>
+        <v>-3.703262232671911</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.295958394401879</v>
+        <v>-3.278307104990944</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.393846016118815</v>
+        <v>-1.676007390928994</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.076431852751774</v>
+        <v>-3.062974559041557</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.04204869540623</v>
+        <v>-3.02859640668612</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.940135818666405</v>
+        <v>-4.926579772314803</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.168246998705385</v>
+        <v>-6.178676634403537</v>
       </c>
     </row>
     <row r="23">
@@ -1459,150 +1459,150 @@
         <v>168</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-5.455280427624764</v>
+        <v>-5.442758137949141</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6587971224158409</v>
+        <v>0.671706931991892</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.864907961328676</v>
+        <v>-6.851900829911074</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.361799683094837</v>
+        <v>-4.344990214271689</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.899677927711274</v>
+        <v>-4.886567123336334</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.196264790915556</v>
+        <v>-5.183221894621191</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.089592588538594</v>
+        <v>-4.076526334238117</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.18197409273364</v>
+        <v>-2.164493436839784</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.43780950104162</v>
+        <v>-3.419086352936525</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.097458495593365</v>
+        <v>-3.084053367940534</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.706973724672849</v>
+        <v>-2.693516430962632</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.267828662565513</v>
+        <v>-3.254376373845403</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.497607083034225</v>
+        <v>-2.484051036682622</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.438361941234128</v>
+        <v>-3.44879157693228</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 64.63</t>
+          <t>X ≈ 64.62</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>160</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.202531806530821</v>
+        <v>-2.190009516855199</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.067699811287063</v>
+        <v>-5.054790001711012</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.343577261249635</v>
+        <v>-2.330570129832033</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.008234474571523265</v>
+        <v>-0.3290161431329111</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.401488674214328</v>
+        <v>-2.388377869839388</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.016504864924983</v>
+        <v>1.029547761219348</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.430842164817371</v>
+        <v>3.443908419117847</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.71485074559115</v>
+        <v>1.730334179996106</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.651476213244088</v>
+        <v>1.66756489228726</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.67635102821616</v>
+        <v>2.689756155868992</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.02840229610141876</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.255980861244005</v>
+        <v>1.269433149964115</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2107262502991105</v>
+        <v>0.2242822966507134</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 67.35</t>
+          <t>X ≈ 67.34</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>149</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.149172903081734</v>
+        <v>-2.136650613406111</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.078296734555877</v>
+        <v>-1.065386924979826</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.143374814382355</v>
+        <v>-2.130367682964753</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6734357937560276</v>
+        <v>-0.6604566513575634</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.880454093487728</v>
+        <v>-1.867343289112789</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.106401453202572</v>
+        <v>3.119444349496938</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.36487134446616</v>
+        <v>4.377937598766636</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.569455759743924</v>
+        <v>4.582983760156537</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.83687889780785</v>
+        <v>3.851787292652752</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.9733308939879706</v>
+        <v>0.9867360216408017</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7685775696703914</v>
+        <v>0.7820348633806091</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.223884910568067</v>
+        <v>-3.210432621847957</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.644139521512969</v>
+        <v>-3.630583475161366</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.7098544308474217</v>
+        <v>-0.7202840665455739</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1052289935646797</v>
+        <v>-0.3772446401980574</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.277584536340676</v>
+        <v>-5.570563882754087</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-9.830336664365362</v>
+        <v>-10.14812452936788</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.355076160573844</v>
+        <v>-4.640869312606185</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.297575722942717</v>
+        <v>-4.579681322238557</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.377331282020727</v>
+        <v>-6.673735337490271</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.270025054067588</v>
+        <v>-5.559294181679036</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.529824798264258</v>
+        <v>-7.816152617233591</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7.009238072470197</v>
+        <v>-7.291819828669254</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-4.287934686069484</v>
+        <v>-4.56323785610698</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-6.278402296101483</v>
+        <v>-6.564346199996059</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.244019138755924</v>
+        <v>-6.529968047640736</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.497607083034161</v>
+        <v>-2.758502134487074</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.652647655519772</v>
+        <v>-1.933964089050832</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.091873743229712</v>
+        <v>-0.7448377976005176</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.005001670448529</v>
+        <v>-1.66236147339422</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.783566815390557</v>
+        <v>-3.431276962916513</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.119976928541107</v>
+        <v>-6.743826241743257</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.114540873693748</v>
+        <v>-1.776477624051417</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.89594232678283</v>
+        <v>-3.543614934010286</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.204761439707511</v>
+        <v>-0.8715245290971652</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4019867842734115</v>
+        <v>0.7297625462272421</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.498698435466274</v>
+        <v>4.794244027814294</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.56523991710489</v>
+        <v>1.870790638627447</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.138264370565409</v>
+        <v>4.424710170022749</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.561536416799491</v>
+        <v>5.838398667205581</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.530170694743475</v>
+        <v>6.79755815871976</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.391003138130877</v>
+        <v>5.643983464118548</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.552741029119787</v>
+        <v>5.680051033474086</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>10.25535071070775</v>
+        <v>9.760037877036545</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>12.66740600857928</v>
+        <v>12.92545039699211</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.990037278968266</v>
+        <v>9.494780342687939</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12.96655178923535</v>
+        <v>12.52165374657685</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>11.15461357709718</v>
+        <v>10.67950322611193</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>13.16879214342175</v>
+        <v>12.72364801921559</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>12.43726173782188</v>
+        <v>12.24662127088053</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.97365931183568</v>
+        <v>11.21484285159852</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.419308774695111</v>
+        <v>9.654041870154785</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.62300615460273</v>
+        <v>10.87791214046585</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.840487903497532</v>
+        <v>8.055147435678414</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.603331884101927</v>
+        <v>4.777853725222144</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.853053216378214</v>
+        <v>5.003589375448676</v>
       </c>
     </row>
     <row r="29">
@@ -1768,153 +1768,153 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>10.36407598036202</v>
+        <v>10.16600031956633</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>12.90486846204157</v>
+        <v>13.45754986630573</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.67146621410335</v>
+        <v>11.41960993248505</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.13895283605043</v>
+        <v>10.73271246943961</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.939065162319949</v>
+        <v>8.560177703076121</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.565940277362593</v>
+        <v>7.214383183645609</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.965605936065415</v>
+        <v>9.573392070740013</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.478921757252721</v>
+        <v>8.268804624210027</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>10.66046504984567</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.759684361549532</v>
+        <v>9.513526647672322</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.888264370565253</v>
+        <v>7.669481227117004</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.089314194577341</v>
+        <v>6.884187248324778</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.835726250299111</v>
+        <v>5.644364263863828</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>5.87009991409036</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 80.94</t>
+          <t>X ≈ 80.93</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>7.506561679790067</v>
+        <v>8.002954937207626</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.494988066825762</v>
+        <v>3.972414005434104</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.900119360229198</v>
+        <v>4.384094233582267</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.230372492836629</v>
+        <v>7.740125828783484</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.491951277764485</v>
+        <v>3.976029824074935</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.189393215480237</v>
+        <v>6.692758692419766</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.904659498207891</v>
+        <v>7.41449994605675</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.837476099426389</v>
+        <v>9.366786140979691</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>12.77647621324412</v>
+        <v>13.33806204897304</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.526351028216112</v>
+        <v>10.06878841393346</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>9.32159770389859</v>
+        <v>9.864087255673311</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.555980861243967</v>
+        <v>9.092013795125403</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.935726250299112</v>
+        <v>5.446056490199098</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.78544758257544</v>
+        <v>11.31695343074821</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 83.66</t>
+          <t>X ≈ 83.65</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.5326540064844778</v>
+        <v>-1.024605350922705</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.738125321727736</v>
+        <v>3.189451274460048</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.382472301405613</v>
+        <v>0.8529323168894933</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-5.350019664026071</v>
+        <v>-5.812959044376505</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.947264408509973</v>
+        <v>-3.438627238248905</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.669430313931628</v>
+        <v>-2.170379422206068</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.147796753109859</v>
+        <v>2.599279150566616</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.52375060923031</v>
+        <v>9.899200798042024</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.52157425245975</v>
+        <v>6.925597282295932</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>13.53419416547106</v>
+        <v>12.87179499082045</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.32944084115348</v>
+        <v>12.66709383256025</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.38343184163622</v>
+        <v>11.73059819850781</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>9.368699772378875</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.33054562179106</v>
+        <v>5.710940276974362</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>83</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.686209404547327</v>
+        <v>-0.6736871148717043</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.297783017511605</v>
+        <v>-2.284873207935554</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.9218061072171295</v>
+        <v>0.9348132386347316</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.767217868609109</v>
+        <v>-3.754238726210644</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.71527763789814</v>
+        <v>-6.702166833523201</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-8.827474254399384</v>
+        <v>-8.814431358105018</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.912207971671592</v>
+        <v>-8.899141717371116</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.174572093344693</v>
+        <v>-8.161391084049455</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.030752702418532</v>
+        <v>-7.017553963463769</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-7.880877887446459</v>
+        <v>-7.867472759793628</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.49526976598094</v>
+        <v>-10.48181247227072</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-5.64160950020181</v>
+        <v>-5.6281572114817</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.676321942471972</v>
+        <v>-9.662765896120369</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-11.83623916441262</v>
+        <v>-11.84666880011077</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>60</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.173228346456696</v>
+        <v>9.185750636132319</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.56165473349246</v>
+        <v>7.574564543068512</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.166786026895849</v>
+        <v>7.179793158313451</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.425284611097865</v>
+        <v>3.438395415472804</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.722726548813576</v>
+        <v>8.735769445107941</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.97132616487449</v>
+        <v>1.984392419174966</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.50414276609304</v>
+        <v>6.517323775388277</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.109809546577367</v>
+        <v>3.12300828553213</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.926351028216118</v>
+        <v>8.939756155868949</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.05493103723191</v>
+        <v>12.06838833094213</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.42264752791074</v>
+        <v>15.43609981663085</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.0023929169658</v>
+        <v>15.0159489633174</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>15.25211424924211</v>
+        <v>15.24168461354396</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 91.81</t>
+          <t>X ≈ 91.8</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>66</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.955594127431823</v>
+        <v>1.968503937007874</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.560725420835247</v>
+        <v>1.573732552252849</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.751584614048802</v>
+        <v>7.764563756447266</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.213163398976619</v>
+        <v>7.226274203351558</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.480302306389241</v>
+        <v>4.493345202683606</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.425871619420036</v>
+        <v>7.438937873720512</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.473839735790044</v>
+        <v>8.487020745085282</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.927991364759244</v>
+        <v>9.941190103714007</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.16877527064041</v>
+        <v>18.18218039829324</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.9337189160198</v>
+        <v>14.94717620973002</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.02870813397124</v>
+        <v>21.04216042269135</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>23.63875655332939</v>
+        <v>23.652312599681</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>22.37332637045417</v>
+        <v>22.36289673475601</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-10 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-10 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2217,46 +2217,46 @@
         <v>4085</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.0328003910421657</v>
+        <v>0.03250515052958036</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.003449433174232297</v>
+        <v>-0.003744788963082613</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0676462075363915</v>
+        <v>-0.06792819585322007</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07590253680346137</v>
+        <v>0.07558606746957253</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.009441343784480694</v>
+        <v>-0.009740067347607351</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1059132545808481</v>
+        <v>0.1055878342275065</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1812177969123567</v>
+        <v>0.1808733575914516</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.06974993805719976</v>
+        <v>0.06943002487904693</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2179044353032751</v>
+        <v>0.2175478128345461</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2130437875116584</v>
+        <v>0.212683521973176</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2667408406737266</v>
+        <v>0.266366152207631</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1191722464618294</v>
+        <v>0.1188336882562737</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1288719051338774</v>
+        <v>0.1285285032097008</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.133795195794491</v>
+        <v>0.1233655600963388</v>
       </c>
     </row>
     <row r="7">
@@ -2269,46 +2269,46 @@
         <v>4035</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1336656490955761</v>
+        <v>-0.1340780858703283</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.02252143311346089</v>
+        <v>0.02205651242850593</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.136469020487759</v>
+        <v>-0.1368982241218788</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.04222889193087553</v>
+        <v>-0.04268050320737871</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1219987593366483</v>
+        <v>-0.1224354450613419</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.008924449042346794</v>
+        <v>-0.009386792009777878</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.005907193205125338</v>
+        <v>-0.006371229183862681</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.01074342615906687</v>
+        <v>0.01027106566298386</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2605069139125717</v>
+        <v>0.2599719819018276</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2413584576366645</v>
+        <v>0.2408207758244245</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3478052837846377</v>
+        <v>0.3472392472373258</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1980026650101223</v>
+        <v>0.1974737741900299</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.213049670373465</v>
+        <v>0.2125132183553688</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2149395280524686</v>
+        <v>0.2045098923543165</v>
       </c>
     </row>
     <row r="8">
@@ -2321,46 +2321,46 @@
         <v>3967</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2943933340325415</v>
+        <v>-0.2949863822931533</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1331667848584956</v>
+        <v>-0.1338211484788019</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3887415902359947</v>
+        <v>-0.3893370578755935</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3454826379480238</v>
+        <v>-0.3460876406009135</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3671682190908427</v>
+        <v>-0.3677749399933461</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2069832314247151</v>
+        <v>-0.2076267813072263</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1773440255776606</v>
+        <v>-0.1779964417543454</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1272771734839822</v>
+        <v>-0.1279484789954637</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1277731157875337</v>
+        <v>0.1270364829138515</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1983913304831617</v>
+        <v>0.1976257101374372</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3857448442361999</v>
+        <v>0.3849290530244147</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1571905386633645</v>
+        <v>0.1564323941062256</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2048969082270133</v>
+        <v>0.2041210063281369</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2025385833316378</v>
+        <v>0.1921089476334856</v>
       </c>
     </row>
     <row r="9">
@@ -2373,46 +2373,46 @@
         <v>3886</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2102161549970489</v>
+        <v>-0.2111032580285794</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1404237884475208</v>
+        <v>-0.1413581523308665</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2134330011671253</v>
+        <v>-0.214356187337053</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2232860437486863</v>
+        <v>-0.2242048329373461</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3634873401968761</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2823252535668388</v>
+        <v>-0.283234150166912</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2246313548239627</v>
+        <v>-0.2255570628011583</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1381085831744855</v>
+        <v>-0.1390653989864887</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1235199150435662</v>
+        <v>0.1224942788500982</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3161684620037661</v>
+        <v>0.3150774926299249</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4860009960796461</v>
+        <v>0.4848621459759954</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.329173554838043</v>
+        <v>0.3280751252727683</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4381451900829489</v>
+        <v>0.4370106218372314</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.430532502801853</v>
+        <v>0.4201028671037008</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3796</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3663374798738346</v>
+        <v>-0.3675004358900864</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1255005068542943</v>
+        <v>-0.1267659891444026</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3485406502805475</v>
+        <v>-0.3497576691097208</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3617431444826451</v>
+        <v>-0.3629541976602937</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.5179330545173073</v>
+        <v>-0.5191166300813137</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4428444915931919</v>
+        <v>-0.4440412804441891</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3292174086832205</v>
+        <v>-0.3304467428899969</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.150684910834066</v>
+        <v>-0.151973085912779</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.09226568692829318</v>
+        <v>0.09091146890498436</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.335932497023741</v>
+        <v>0.3344929979742588</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4883170298596156</v>
+        <v>0.4868317809728353</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4059676929532543</v>
+        <v>0.4045042400115193</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.5011635527227156</v>
+        <v>0.4996641770826358</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4611061705627506</v>
+        <v>0.4506765348645985</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3680</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2853646274437835</v>
+        <v>-0.2869832027987087</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.03997128276773054</v>
+        <v>-0.0417092761313711</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2846461588816922</v>
+        <v>-0.286331502933173</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2752674203954228</v>
+        <v>-0.2769519700779526</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3921821640581058</v>
+        <v>-0.3938533191620763</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2969876852252042</v>
+        <v>-0.2986759034139723</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.1516177092387778</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.02205807553931294</v>
+        <v>0.02026362161171846</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2204077907624153</v>
+        <v>0.2185566025788717</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5531842710189778</v>
+        <v>0.5512142063712986</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.6354798011547658</v>
+        <v>0.6334797667560039</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6038069482005355</v>
+        <v>0.6018156547182656</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6998566850817198</v>
+        <v>0.7134127314333227</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6234910608362654</v>
+        <v>0.6130614251381132</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3549</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3866967471762663</v>
+        <v>-0.3888070723765296</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3820560466892644</v>
+        <v>-0.3842369550588529</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3683460697876768</v>
+        <v>-0.3705486980132306</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2791017832386657</v>
+        <v>-0.2813251494753715</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4929756063749764</v>
+        <v>-0.4951628264914234</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3208740137744073</v>
+        <v>-0.3230981964369306</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1652335800138331</v>
+        <v>-0.1675063150021856</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.05841615008780821</v>
+        <v>0.05605947225567576</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2663410781089581</v>
+        <v>0.2639220673128335</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3893192061941946</v>
+        <v>0.3868282279410593</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4258230560112608</v>
+        <v>0.4233118266710321</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.4480067840391655</v>
+        <v>0.4454894879922904</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5349372956640082</v>
+        <v>0.5484933420156111</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4747121641476753</v>
+        <v>0.4642825284495231</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3401</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.178080758662496</v>
+        <v>-0.1808867307980435</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3084713292457693</v>
+        <v>-0.3113283838561003</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1890301998881228</v>
+        <v>-0.1919453347970759</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1015136907948886</v>
+        <v>-0.1044489512751241</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4772975485265647</v>
+        <v>-0.4801535236100349</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1638794584264929</v>
+        <v>-0.1668127145165386</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1151878300363904</v>
+        <v>-0.1181415794552407</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2266097264454814</v>
+        <v>0.2235285121273805</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3287676351007249</v>
+        <v>0.3256514573383598</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5234712162855075</v>
+        <v>0.5202496928842635</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.570510108366534</v>
+        <v>0.5672618738944308</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.621608617786201</v>
+        <v>0.6183455544320751</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7600132247183993</v>
+        <v>0.7735692710700022</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7451065064213225</v>
+        <v>0.7346768707231703</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3238</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2004250853684866</v>
+        <v>-0.2039929536112766</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4104306523860544</v>
+        <v>-0.414047337510155</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3267977940670974</v>
+        <v>-0.3304695674665226</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1798554800530283</v>
+        <v>-0.1835655190611334</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.609127304670011</v>
+        <v>-0.612744448975775</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1099902617084894</v>
+        <v>-0.113742624743189</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.02374013176435597</v>
+        <v>-0.02752702184428557</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2662237860395891</v>
+        <v>0.2623129829121993</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3457449574588409</v>
+        <v>0.3418032680532619</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5621534973519573</v>
+        <v>0.5580838325120041</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8379916526481921</v>
+        <v>0.8338204297075649</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.7047146475318442</v>
+        <v>0.7005847399610303</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8403587394899645</v>
+        <v>0.8539147858415674</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.8430139815871343</v>
+        <v>0.8325843458889821</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3071</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.08689274113374523</v>
+        <v>0.08235457296986937</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5335833617456629</v>
+        <v>-0.5380612277851355</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4888380934895622</v>
+        <v>-0.4933670148467257</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3735261426409053</v>
+        <v>-0.3780838957814225</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7644023133957205</v>
+        <v>-0.768882037418706</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2868096453780922</v>
+        <v>-0.2914215417841248</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2888364367514598</v>
+        <v>-0.2934576024981368</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1400135099664013</v>
+        <v>0.1352099542500866</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2271758552876975</v>
+        <v>0.2223359801754299</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3716635282161604</v>
+        <v>0.3667005099204061</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5760425101506144</v>
+        <v>0.570992497608799</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.2522361526800267</v>
+        <v>0.2656884414001368</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.3529844723766047</v>
+        <v>0.3665405187282076</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5375804383227134</v>
+        <v>0.5271508026245613</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2914</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.06525774565456999</v>
+        <v>-0.05273545597894724</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6325521316005052</v>
+        <v>-0.6379297569771154</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5984432681075802</v>
+        <v>-0.6038765873816132</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4497370586867717</v>
+        <v>-0.4552109931016162</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6272268044272735</v>
+        <v>-0.6326989586000309</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.07138102227248311</v>
+        <v>-0.07701594301998682</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.06888402475304645</v>
+        <v>-0.07453186996508521</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4768316016547018</v>
+        <v>0.4709449771246454</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.640673744108291</v>
+        <v>0.6347212326239458</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7359565170669242</v>
+        <v>0.7298796126591114</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.168406214536887</v>
+        <v>1.162156198294902</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.9625697425068793</v>
+        <v>0.9760220312269894</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.85116894075896</v>
+        <v>0.8647249871105629</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.826353553749037</v>
+        <v>0.8159239180508848</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2736</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.01930749188033332</v>
+        <v>0.03182978155595606</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3345201298955445</v>
+        <v>-0.3411917084488678</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6004637301498335</v>
+        <v>-0.6070920875881924</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5599300955701736</v>
+        <v>-0.5665609012080139</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.5316811073558441</v>
+        <v>-0.5383939878569137</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.04098022751957586</v>
+        <v>0.03409183752216194</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1221777463830662</v>
+        <v>0.1152449061019425</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5877499219893707</v>
+        <v>0.5805841160209013</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8758187990731585</v>
+        <v>0.8685358503368548</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.178817232089017</v>
+        <v>1.171312036073523</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.360486592787467</v>
+        <v>1.352884738200686</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.431419457735238</v>
+        <v>1.444871746455348</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.084264261995017</v>
+        <v>1.09782030834662</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.187786763861951</v>
+        <v>1.177357128163798</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2544</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.0515890877774936</v>
+        <v>0.06411137745311635</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2859755054421527</v>
+        <v>-0.2941381455245633</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.307090671118786</v>
+        <v>-0.3153106411381827</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6651978717262423</v>
+        <v>-0.673262784827557</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6727546045884338</v>
+        <v>-0.6809042055908563</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.236342367101237</v>
+        <v>-0.2446227117548716</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2212431705519222</v>
+        <v>-0.229547688056563</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5108172851350687</v>
+        <v>0.5021484744987106</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7073481692535211</v>
+        <v>0.6985873982137747</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.254445330770181</v>
+        <v>1.245333532145509</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.465308395722481</v>
+        <v>1.456076608610765</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.57830790526917</v>
+        <v>1.59176019398928</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.000820589921759</v>
+        <v>1.014376636273361</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.329158274399298</v>
+        <v>1.318728638701145</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2361</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2714413758643204</v>
+        <v>0.2839636655399431</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1179610397987361</v>
+        <v>0.1079823002093363</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.0187004413102656</v>
+        <v>0.03170757272786773</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1237466453128704</v>
+        <v>-0.1336753917918898</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1215370765810775</v>
+        <v>0.1113992177541476</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.08085559925024199</v>
+        <v>0.09389849554460739</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3575136208294509</v>
+        <v>0.3473115513249354</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.098051395534682</v>
+        <v>1.087443578066242</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.653327673252548</v>
+        <v>1.642466830371447</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.97038151085799</v>
+        <v>1.959222935386549</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.171407106694005</v>
+        <v>2.160118503112606</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.07872546098988</v>
+        <v>2.09217774970999</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.446696178295724</v>
+        <v>1.460252224647327</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.908192182321265</v>
+        <v>1.897762546623113</v>
       </c>
     </row>
     <row r="20">
@@ -2945,98 +2945,98 @@
         <v>2143</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7871573056625181</v>
+        <v>0.7996795953381408</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5250485600784387</v>
+        <v>0.5379583696544898</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.05595323167403166</v>
+        <v>-0.04294610025642953</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.05309130103034931</v>
+        <v>0.04074577204296048</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.04079208506735199</v>
+        <v>-0.05322469625906479</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2091163327266301</v>
+        <v>-0.1960734364322647</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9430565159152522</v>
+        <v>0.9302082862764109</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.527452789403085</v>
+        <v>1.514217220557605</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.285804571453042</v>
+        <v>2.272192434716331</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.535777066480271</v>
+        <v>2.521845708107797</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.471014409451541</v>
+        <v>2.484471703161759</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.365406899508123</v>
+        <v>2.378859188228233</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.805161621274372</v>
+        <v>1.818717667625975</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.381527843891305</v>
+        <v>2.371098208193153</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 55.12</t>
+          <t>X &gt; 55.11</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.289792763634608</v>
+        <v>1.325931184590836</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6495892938196306</v>
+        <v>0.685618877934786</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.05202787903463246</v>
+        <v>-0.06684284918101469</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3618302933481843</v>
+        <v>0.3188753960936026</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1584814722373835</v>
+        <v>0.1152870310147023</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.09768390125294246</v>
+        <v>0.08274301714538268</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.628264208909371</v>
+        <v>1.583710407239828</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.958377738770643</v>
+        <v>1.913093137380784</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.798003635079048</v>
+        <v>2.751784527211647</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.105838207703336</v>
+        <v>3.058608614885379</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.003648985949866</v>
+        <v>2.986720810012699</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.986750092013246</v>
+        <v>3.021098962368022</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.36136727594014</v>
+        <v>2.34466927768608</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.611088608216427</v>
+        <v>2.621660694186318</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1774</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.300828121611275</v>
+        <v>1.313350411286898</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.263172440069155</v>
+        <v>1.276082249645206</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4186128959233884</v>
+        <v>0.4316200273409905</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.8609686683147402</v>
+        <v>0.8429019443975889</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5787267420301205</v>
+        <v>0.5606301361327013</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8198940595994699</v>
+        <v>0.8329369558938353</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.592222807155558</v>
+        <v>2.605289061456034</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.05819682014711</v>
+        <v>3.038614340010319</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.48070156535676</v>
+        <v>3.460846123370018</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.960172899693049</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.417200860606577</v>
+        <v>3.430658154316795</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.620693375336458</v>
+        <v>3.634145664056568</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.9749596212123</v>
+        <v>2.988515667563902</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.337420525078215</v>
+        <v>3.326990889380063</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1571</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.254973369751909</v>
+        <v>1.267495659427532</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.549371802530985</v>
+        <v>1.562281612107036</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.582711482211387</v>
+        <v>0.5957186136289891</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.129418900973995</v>
+        <v>1.10713816636602</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.9724344309749355</v>
+        <v>0.9855452353498748</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.524167532072667</v>
+        <v>1.537210428367032</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.28304474932041</v>
+        <v>3.296111003620886</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.934168211385682</v>
+        <v>3.909779804207957</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.356361636541351</v>
+        <v>4.331659685023276</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.652003478884524</v>
+        <v>4.665408606537355</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.256288983338429</v>
+        <v>4.269746277048647</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.481633311912375</v>
+        <v>4.495085600632486</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.997724977224635</v>
+        <v>4.011281023576238</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.565714928215115</v>
+        <v>4.555285292516963</v>
       </c>
     </row>
     <row r="24">
@@ -3153,150 +3153,150 @@
         <v>1403</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.058482021184048</v>
+        <v>2.071004310859671</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.656012248902577</v>
+        <v>1.668922058478628</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.47451480830884</v>
+        <v>1.487521939726442</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.786956122729919</v>
+        <v>1.759994593983365</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.675581171002939</v>
+        <v>1.688691975377878</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.328894994839608</v>
+        <v>2.341937891133973</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.165869462620698</v>
+        <v>4.178935716921174</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.666535928486219</v>
+        <v>4.637133977049025</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.28966224317994</v>
+        <v>5.259760422284316</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.579950458009463</v>
+        <v>5.593355585662295</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.090093783727518</v>
+        <v>5.103551077437736</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.409580291037315</v>
+        <v>5.423032579757425</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.775498167619141</v>
+        <v>4.789054213970743</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.52415036233306</v>
+        <v>5.513720726634908</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 65.99</t>
+          <t>X &gt; 65.98</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1243</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.606963286215723</v>
+        <v>2.619485575891346</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.521494090922161</v>
+        <v>2.534403900498212</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.965982814044438</v>
+        <v>1.97898994546204</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.015914661511374</v>
+        <v>2.028893803909838</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.200385012704267</v>
+        <v>2.213495817079206</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.497826950419928</v>
+        <v>2.510869846714293</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.260482791380582</v>
+        <v>4.273549045681058</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.046479314860477</v>
+        <v>5.011299679002747</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.757972592970553</v>
+        <v>5.722150836443227</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.953704206011814</v>
+        <v>5.967109333664645</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.748950881694235</v>
+        <v>5.762408175404452</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.944235084896462</v>
+        <v>5.957687373616572</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.363079428094764</v>
+        <v>5.376635474446367</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.773701806227848</v>
+        <v>5.763272170529696</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 68.71</t>
+          <t>X &gt; 68.7</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1094</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.254736862271777</v>
+        <v>3.2672591519474</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.011776387993656</v>
+        <v>3.024686197569707</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.525666805484654</v>
+        <v>2.538673936902256</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.382197310354925</v>
+        <v>2.39517645275339</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.75618485440684</v>
+        <v>2.769295658781779</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.414940660735645</v>
+        <v>2.427983557030011</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.246265337623946</v>
+        <v>4.259331591924422</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.111448702166115</v>
+        <v>5.069635210911407</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.019620637375709</v>
+        <v>5.976889564070994</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.632018304267355</v>
+        <v>6.645423431920186</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.427264979949776</v>
+        <v>6.440722273659993</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.192909563254979</v>
+        <v>7.206361851975089</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.589839595820131</v>
+        <v>6.603395642171733</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.656745571606479</v>
+        <v>6.646315935908326</v>
       </c>
     </row>
     <row r="27">
@@ -3306,49 +3306,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.864320300479683</v>
+        <v>3.923820245030775</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.515677721998173</v>
+        <v>4.573129308048756</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.767360739539519</v>
+        <v>4.824213682174225</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.604510423871162</v>
+        <v>3.662727308001557</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.035916795005889</v>
+        <v>4.093221393226642</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.010082870652575</v>
+        <v>4.067667543421472</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.972762946483755</v>
+        <v>6.028167087276941</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.404897890149158</v>
+        <v>7.391023093651661</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.383387660328324</v>
+        <v>8.367261159095406</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.613176082211837</v>
+        <v>8.664675249720119</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.732396839967706</v>
+        <v>8.783598686929196</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.63071088284228</v>
+        <v>9.680975760535866</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.238534025677076</v>
+        <v>8.289951120814692</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.164281275879929</v>
+        <v>8.192062175571955</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>782</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.776969843055333</v>
+        <v>4.789492132730956</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.716416638254337</v>
+        <v>5.729326447830388</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.341956094923056</v>
+        <v>6.354963226340658</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.579352084673417</v>
+        <v>5.592331227071881</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.168481890009403</v>
+        <v>5.181592694384342</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.465923827725064</v>
+        <v>5.478966724019429</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.294455416575239</v>
+        <v>7.307521670875715</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.69443650811094</v>
+        <v>8.626167312803261</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.098726852630286</v>
+        <v>9.029777123335506</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.911005759673969</v>
+        <v>9.9244108873268</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.578375197504712</v>
+        <v>9.59183249121493</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.38002178196012</v>
+        <v>10.39347407068023</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.553117554646938</v>
+        <v>8.566673600998541</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.674961649071562</v>
+        <v>8.66453201337341</v>
       </c>
     </row>
     <row r="29">
@@ -3410,153 +3410,153 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.604845611147276</v>
+        <v>4.595289257179495</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.709340640928737</v>
+        <v>4.850355108128106</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.93849689533058</v>
+        <v>4.922146709376172</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.60073130718925</v>
+        <v>4.7413298622958</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.438285131118647</v>
+        <v>3.580956327862616</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.203745789583138</v>
+        <v>4.344893343500821</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.991086955306173</v>
+        <v>6.126434928247093</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.863997160268823</v>
+        <v>7.836660219141535</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.682726213244088</v>
+        <v>8.553283039290612</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.02010102821616</v>
+        <v>9.983369863034099</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.346597703898581</v>
+        <v>9.311378985147741</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>10.94348086124401</v>
+        <v>10.90338953625696</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.429476250299111</v>
+        <v>9.392896003815821</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.522947582575398</v>
+        <v>9.462868414166969</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 79.58</t>
+          <t>X &gt; 79.57</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>520</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.275792449020798</v>
+        <v>3.288314738696421</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.818064989902688</v>
+        <v>2.830974799478739</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.384734744844565</v>
+        <v>3.397741876262167</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.322680185144364</v>
+        <v>3.335659327542828</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.399643585456815</v>
+        <v>2.412754389831754</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.658623984710943</v>
+        <v>3.671666881005308</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.722091484041776</v>
+        <v>7.735272493337014</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.045706982474854</v>
+        <v>8.058905721429618</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.08019718206231</v>
+        <v>10.09360230971514</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>9.683136165437048</v>
+        <v>9.696593459147266</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.83290393816709</v>
+        <v>11.8463562268872</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.25880317337603</v>
+        <v>10.27235921972763</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.31621681334462</v>
+        <v>10.30578717764647</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 82.3</t>
+          <t>X &gt; 82.29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.936941426625467</v>
+        <v>1.812013262394942</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.603848826319442</v>
+        <v>2.473554442058379</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.221638347570945</v>
+        <v>3.088884067404358</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.086068695368326</v>
+        <v>1.956482948366457</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.05397659422021</v>
+        <v>1.923243900321268</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.857747645859909</v>
+        <v>2.725668435006853</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.798330384283837</v>
+        <v>4.661160095942705</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.369121669046642</v>
+        <v>7.224394482458997</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.54862811197826</v>
+        <v>6.405836568360463</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.25546495226679</v>
+        <v>10.10137231748516</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.797547070987193</v>
+        <v>9.644145906699706</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.86990491187693</v>
+        <v>12.70882708935806</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.94332118700797</v>
+        <v>11.78362573099415</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.16772606358805</v>
+        <v>9.989159361018658</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>293</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.796664068868523</v>
+        <v>2.809186358544146</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.208981240887205</v>
+        <v>2.221891050463256</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.861894104256486</v>
+        <v>3.874901235674088</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.674741093519273</v>
+        <v>4.687720235917737</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.795022950119453</v>
+        <v>3.808133754494392</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.433761816162765</v>
+        <v>4.44680471245713</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.372918883873425</v>
+        <v>5.385985138173901</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.2709231984025</v>
+        <v>6.284104207697737</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.209923312220198</v>
+        <v>6.223122051174961</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.114064338796368</v>
+        <v>9.127469466449199</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.568014086151138</v>
+        <v>8.581471379861355</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.03925731175596</v>
+        <v>13.05270960047607</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.61900270081106</v>
+        <v>12.63255874716266</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.50353631977676</v>
+        <v>11.4931066840786</v>
       </c>
     </row>
     <row r="33">
@@ -3621,150 +3621,150 @@
         <v>210</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.173228346456689</v>
+        <v>4.185750636132312</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.99022616206387</v>
+        <v>4.003135971639921</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.023928884038703</v>
+        <v>5.036936015456305</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.011324873789057</v>
+        <v>8.024304016187521</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.949094134907362</v>
+        <v>7.962204939282302</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.0189452124936</v>
+        <v>11.03201146679407</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.98033324228353</v>
+        <v>11.99351425157877</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>15.83111293297806</v>
+        <v>15.84451806063089</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>16.10255008485096</v>
+        <v>16.11600737856118</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>20.42264752791068</v>
+        <v>20.43609981663079</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>21.43096434553721</v>
+        <v>21.44452039188882</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>20.72830472543255</v>
+        <v>20.7178750897344</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 90.45</t>
+          <t>X &gt; 90.44</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>150</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.173228346456689</v>
+        <v>2.185750636132312</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.561654733492432</v>
+        <v>2.574564543068483</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.166786026895842</v>
+        <v>4.179793158313444</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.630372492836678</v>
+        <v>9.643351635235142</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.758617944431165</v>
+        <v>9.771728748806105</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.05605988214683</v>
+        <v>10.06910277844119</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.63799283154123</v>
+        <v>14.65105908584171</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>14.17080943275973</v>
+        <v>14.18399044205497</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.77647621324409</v>
+        <v>14.78967495219885</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.59301769488283</v>
+        <v>18.60642282253566</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.72159770389858</v>
+        <v>17.7350549976088</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>22.42264752791067</v>
+        <v>22.43609981663078</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>24.00239291696577</v>
+        <v>24.01594896331737</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>22.91878091590873</v>
+        <v>22.90835128021057</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 93.17</t>
+          <t>X &gt; 93.16</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>5.852417302798983</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.214405074514886</v>
+        <v>6.227412205932488</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>11.10656296902716</v>
+        <v>11.11954211142562</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.7717287488061</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>14.43701226309922</v>
+        <v>14.45005515939359</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20.30465949820789</v>
+        <v>20.31772575250837</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>18.6469999089502</v>
+        <v>18.66018091824544</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>18.5860000227679</v>
+        <v>18.59919876172266</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18.92635102821616</v>
+        <v>18.93975615586899</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>19.91207389437477</v>
+        <v>19.92553118808499</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>23.51788562314879</v>
+        <v>23.5313379118689</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>24.28810720268006</v>
+        <v>24.30166324903166</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>23.34735234448017</v>
+        <v>23.33692270878202</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-10 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-10 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3908,49 +3908,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.302962129733785</v>
+        <v>-1.290439840058163</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.023928884038703</v>
+        <v>5.036936015456305</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.798198935734753</v>
+        <v>-0.7852197933362888</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.425284611097844</v>
+        <v>3.438395415472783</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.039178213091262</v>
+        <v>-1.026135316796896</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.50486431131592</v>
+        <v>-3.491798057015444</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4.033047596279722</v>
+        <v>-4.019848857324959</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.692696590831453</v>
+        <v>-3.679291463178622</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2119536066717913</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
@@ -3960,49 +3960,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.222979590237784</v>
+        <v>4.235501879913407</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.865137320557103</v>
+        <v>1.878047130133154</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.201611897542605</v>
+        <v>5.214619028960207</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.093059060000854</v>
+        <v>3.106038202399318</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.539712471794353</v>
+        <v>5.552823276169292</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.852079782644346</v>
+        <v>2.865122678938711</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.513614722088491</v>
+        <v>3.526680976388967</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.04643132330699</v>
+        <v>3.059612332602228</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.730986473323071</v>
+        <v>-3.717787734368308</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.088574344918172</v>
+        <v>-3.075169217265341</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.766407198457479</v>
+        <v>-1.752954909737369</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.186661809402381</v>
+        <v>-2.173105763050778</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.279214071559942</v>
+        <v>-1.947370112824245</v>
       </c>
     </row>
     <row r="8">
@@ -4012,49 +4012,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.922403263948439</v>
+        <v>5.934925553624062</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.310829650984182</v>
+        <v>4.323739460560233</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.37140648894205</v>
+        <v>8.384413620359652</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.006610116599056</v>
+        <v>8.01958925899752</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.458287911427874</v>
+        <v>8.471398715802813</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.785432819440565</v>
+        <v>5.798475715734931</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.700699102168286</v>
+        <v>5.713765356468762</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.738466198436285</v>
+        <v>4.751647207731523</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.22202076769954</v>
+        <v>0.2352195066543032</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.123153922278888</v>
+        <v>-1.109748794626057</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.793253781249931</v>
+        <v>-4.779796487539713</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3034250793500419</v>
+        <v>-0.2899727906299319</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.218729195245437</v>
+        <v>-1.205173148893834</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.190671820409676</v>
+        <v>-0.979437498667302</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.983593481910162</v>
+        <v>2.996115771585785</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.138804321242723</v>
+        <v>3.151714130818775</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.450649395564866</v>
+        <v>3.463656526982469</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.934259418631733</v>
+        <v>3.947238561030197</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.869336436775107</v>
+        <v>5.882447241150047</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.106707703112683</v>
+        <v>5.119750599407048</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.668617095381038</v>
+        <v>4.681683349681514</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.494719915680804</v>
+        <v>3.507900924976042</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2535080153642255</v>
+        <v>0.2667067543189887</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.363401621960513</v>
+        <v>-2.349996494307682</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.688296289034284</v>
+        <v>-4.674838995324066</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.533771788932661</v>
+        <v>-2.520319500212551</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.014097071255662</v>
+        <v>-4.000541024904059</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.932282913878502</v>
+        <v>-3.774805374677527</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3.806829776304774</v>
+        <v>3.819352065980397</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.195256163340517</v>
+        <v>2.208165972916568</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.945159574706381</v>
+        <v>3.958166706123983</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.34350922205919</v>
+        <v>4.356488364457654</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.949860124949488</v>
+        <v>5.962970929324428</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.443012518429228</v>
+        <v>5.456055414723593</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.553989256921021</v>
+        <v>4.567055511221497</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.746323284412988</v>
+        <v>2.759504293708225</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5405512802682182</v>
+        <v>0.5537500192229814</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.918152993231558</v>
+        <v>-1.904747865578727</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.463388891275677</v>
+        <v>-3.44993159756546</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.624716189694325</v>
+        <v>-2.611263900974215</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.581163830129839</v>
+        <v>-3.567607783778236</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.188745965811705</v>
+        <v>-3.073775618806401</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.200439230810431</v>
+        <v>2.212961520486054</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9970288831522893</v>
+        <v>1.00993869272834</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.438894870433266</v>
+        <v>2.451902001850868</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.569148003040766</v>
+        <v>2.58212714543923</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.45929821654002</v>
+        <v>3.472409020914959</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.940413623643437</v>
+        <v>2.953456519937802</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.039353375758914</v>
+        <v>2.05241963005939</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.7558434463651693</v>
+        <v>0.7690244556604071</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5296462357355054</v>
+        <v>-0.5164474967807422</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.012424481987921</v>
+        <v>-2.99901935433509</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.625341071611622</v>
+        <v>-3.611883777901404</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.386876281613127</v>
+        <v>-3.373423992893017</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.108036530886984</v>
+        <v>-4.201738111512554</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.545699958408214</v>
+        <v>-3.459746879298621</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.256964256279559</v>
+        <v>2.269486545955182</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.73878838888696</v>
+        <v>2.751698198463011</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.34391968229037</v>
+        <v>2.356926813707972</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.99108102745825</v>
+        <v>2.004060169856714</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.223996366331342</v>
+        <v>3.237107170706281</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.394224133354562</v>
+        <v>2.407267029648928</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.665368032829463</v>
+        <v>1.678434287129939</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.4062126642771844</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.6341518060795863</v>
+        <v>-0.6209530671248231</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.323246395294305</v>
+        <v>-1.309841267641474</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.527999719611884</v>
+        <v>-1.514542425901666</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.654647158079662</v>
+        <v>-1.641194869359552</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.148144717442825</v>
+        <v>-2.222376318486162</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.810352094322823</v>
+        <v>-1.74756269828405</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8225564782295578</v>
+        <v>0.8350787679051805</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.811763099335529</v>
+        <v>1.82467290891158</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.026777357628397</v>
+        <v>1.039784489045999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.766913455125362</v>
+        <v>0.7798925975238262</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.439155439012886</v>
+        <v>2.452266243387825</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.176129236286407</v>
+        <v>1.189172132580772</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.091395519014128</v>
+        <v>1.104461773314604</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.416099973395454</v>
+        <v>-0.4029189641002162</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7371778829847884</v>
+        <v>-0.7239791440300252</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.587303068012716</v>
+        <v>-1.573897940359885</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.792056392330295</v>
+        <v>-1.778599098620077</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.017751258391876</v>
+        <v>-2.004298969671765</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.627815416367554</v>
+        <v>-2.684527846392193</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.568398571270755</v>
+        <v>-2.518732053122754</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.7254457999616974</v>
+        <v>0.7379680896373202</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.796275620473843</v>
+        <v>1.809185430049894</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.294110776538183</v>
+        <v>1.307117907955785</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.8878832224504123</v>
+        <v>0.9008623648488765</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.388088616820305</v>
+        <v>2.401199421195244</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7542000824329591</v>
+        <v>0.7672429787273245</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5621702278216247</v>
+        <v>0.5752364821221008</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4414938576551606</v>
+        <v>-0.4283128483599228</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.6097898811765177</v>
+        <v>-0.5965911422217545</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.35261892886539</v>
+        <v>-1.339213801212559</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.308445214556357</v>
+        <v>-2.29498792084614</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.844877507854704</v>
+        <v>-1.831425219134594</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.314112632622482</v>
+        <v>-2.358872209787059</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.328530912048258</v>
+        <v>-2.289643707258094</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2207110474827019</v>
+        <v>-0.2081887578070791</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.804078975916674</v>
+        <v>1.816988785492725</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.500119360229185</v>
+        <v>1.513126491646787</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.266736129200318</v>
+        <v>1.279715271598782</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.364678550491782</v>
+        <v>2.377789354866721</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.116665942752896</v>
+        <v>1.129708839047261</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.213750407298797</v>
+        <v>1.226816661599273</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.01929428124456223</v>
+        <v>0.03247529053980003</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1326146958468186</v>
+        <v>-0.1194159568920554</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5281944263292999</v>
+        <v>-0.5147892986764688</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.096584114283246</v>
+        <v>-1.083126820573028</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1930637247432472</v>
+        <v>-0.2305668500358706</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4711954254750239</v>
+        <v>-0.5087704785995086</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9906690992842115</v>
+        <v>-0.9605011788058206</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1716372565601176</v>
+        <v>0.1422954162065082</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.742243436754173</v>
+        <v>1.755153246330224</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.506483719815492</v>
+        <v>1.519490851233094</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.238964378278204</v>
+        <v>1.251943520676669</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.655197101153526</v>
+        <v>1.668307905528465</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4411036371189923</v>
+        <v>0.4541465334133576</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5154789095046297</v>
+        <v>0.5285451638051057</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7472494375664525</v>
+        <v>-0.7340684282712147</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.046912808235625</v>
+        <v>-1.033714069280862</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.260602034631894</v>
+        <v>-1.247196906979063</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.260900307239048</v>
+        <v>-2.24744301352883</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.785420412641336</v>
+        <v>-1.81529238702872</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.524831518625192</v>
+        <v>-1.555176302075402</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.470373789035449</v>
+        <v>-1.44490237184786</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.01957072439116558</v>
+        <v>-0.04359012524187733</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8775664640383098</v>
+        <v>0.890476273614361</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.249248280089802</v>
+        <v>1.262255411507404</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.24012859039766</v>
+        <v>1.253107732796124</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.189512253374268</v>
+        <v>1.202623057749207</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.162912379243231</v>
+        <v>0.1759552755375964</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.07817866197095213</v>
+        <v>0.09124491627142817</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8071232037095015</v>
+        <v>-0.7939421944142637</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.286241556790756</v>
+        <v>-1.273042817835993</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.857621097219372</v>
+        <v>-1.844215969566541</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.201747243836607</v>
+        <v>-2.188289950126389</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.33885874823995</v>
+        <v>-2.362971031220546</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.674741300294045</v>
+        <v>-1.699532208230735</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.875446272173207</v>
+        <v>-1.854151627442363</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0656571278313649</v>
+        <v>-0.08533863495695471</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6583562290875946</v>
+        <v>0.6712660386636458</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5708015974756506</v>
+        <v>0.5838087288932527</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.192757250058563</v>
+        <v>1.205736392457027</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.207501369958727</v>
+        <v>1.220612174333667</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.583001082720493</v>
+        <v>0.5960439790148584</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6211929954420654</v>
+        <v>0.6342592497425414</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.5220813683056349</v>
+        <v>-0.5089003590103971</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7674696994787169</v>
+        <v>-0.7542709605239537</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.617594884506644</v>
+        <v>-1.604189756853813</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.945273838818075</v>
+        <v>-1.931816545107857</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.123477933343935</v>
+        <v>-2.143289652740243</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.218119903547041</v>
+        <v>-1.23866358280808</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.734749461759577</v>
+        <v>-1.717289745430442</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3411204394152705</v>
+        <v>-0.3573639069822363</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.03406091450789006</v>
+        <v>0.04697072408394121</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.05561356232746562</v>
+        <v>0.03851280511256761</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2963029180161314</v>
+        <v>0.3092820604145956</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.02124585089369191</v>
+        <v>-0.008135046518752631</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.08552581216525823</v>
+        <v>0.06836653695398809</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2202023802451478</v>
+        <v>-0.2071361259446718</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.18462334808742</v>
+        <v>-1.171442338792183</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.853358040899558</v>
+        <v>-1.840159301944794</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.261494275651245</v>
+        <v>-2.248089147998414</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.521496218753356</v>
+        <v>-2.508038925043138</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.402117535660352</v>
+        <v>-2.418412153903283</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.575778174479645</v>
+        <v>-1.592674585604669</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.181016169499863</v>
+        <v>-2.166132495600628</v>
       </c>
     </row>
     <row r="20">
@@ -4636,101 +4636,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.8202099737532862</v>
+        <v>-0.833104913957861</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3876313324849221</v>
+        <v>-0.401157241708411</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.1306612321503593</v>
+        <v>0.116770017003752</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.06387002978248546</v>
+        <v>0.07684917218094967</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1658429033802733</v>
+        <v>0.1789537077552126</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3918574835925384</v>
+        <v>0.3778055699026126</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7771542031228194</v>
+        <v>-0.7640879488223433</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.392193688646557</v>
+        <v>-1.37901267935132</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.143188646292629</v>
+        <v>-2.129989907337865</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.401889484351607</v>
+        <v>-2.388484356698775</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.333629120559017</v>
+        <v>-2.34675870372191</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.223298862485635</v>
+        <v>-2.236484009799184</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.629722910609075</v>
+        <v>-1.643317604681307</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.24171291125176</v>
+        <v>-2.229523020546246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 55.12</t>
+          <t>X &lt; 55.11</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.12265180335605</v>
+        <v>-1.155073333905143</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4179615734620015</v>
+        <v>-0.4500157926629242</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1110055500627425</v>
+        <v>0.1240126814803446</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2085838724354758</v>
+        <v>-0.171229822910675</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.02725699933851189</v>
+        <v>0.01055263119435068</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.06986126228484579</v>
+        <v>0.08290415857921118</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.22999396713864</v>
+        <v>-1.192855066942329</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.517159364119969</v>
+        <v>-1.479824656249107</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.208222256602902</v>
+        <v>-2.171153503451755</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.473288935780239</v>
+        <v>-2.435750372721735</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.383760242972201</v>
+        <v>-2.370302949261983</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.370145264882112</v>
+        <v>-2.401738021207045</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.819749189088007</v>
+        <v>-1.806193142736404</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.041243129778067</v>
+        <v>-2.051672765476219</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9530553060551057</v>
+        <v>-0.9619813655322744</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.7938915666602782</v>
+        <v>-0.8031762285107575</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2498806397708222</v>
+        <v>-0.259468260539812</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5362941738299867</v>
+        <v>-0.5233150314315225</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3247153889021632</v>
+        <v>-0.3116045845272239</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4630453005681829</v>
+        <v>-0.4725638882254657</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.734539834569425</v>
+        <v>-1.743549778963079</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.076618979806305</v>
+        <v>-2.063437970511067</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.346125955229638</v>
+        <v>-2.332927216274875</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.695834126079085</v>
+        <v>-2.682428998426253</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.294255445871968</v>
+        <v>-2.303310306811547</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.446022477654154</v>
+        <v>-2.455014075734674</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.966987737174797</v>
+        <v>-1.97626027430087</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.237442977157265</v>
+        <v>-2.228739881932775</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7481372078202568</v>
+        <v>-0.7554559078349641</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.8049351872033981</v>
+        <v>-0.8124703629537606</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.2964257453370465</v>
+        <v>-0.3042180977622806</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5884374879694647</v>
+        <v>-0.5754583455710005</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.491766080146391</v>
+        <v>-0.4995444437722583</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.7880942989262891</v>
+        <v>-0.7957205702531098</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.812942346526931</v>
+        <v>-1.82019203466028</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.203261794501366</v>
+        <v>-2.190080785206128</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.417989582297807</v>
+        <v>-2.404790843343044</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.594217983702329</v>
+        <v>-2.601366057812797</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.355325373024499</v>
+        <v>-2.362599750564982</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.492576276116509</v>
+        <v>-2.499797619266651</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.199300693503815</v>
+        <v>-2.206700773760986</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.544702590701462</v>
+        <v>-2.537376202468401</v>
       </c>
     </row>
     <row r="24">
@@ -4844,153 +4844,153 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.033978860750523</v>
+        <v>-1.03999384033262</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7164034256039287</v>
+        <v>-0.7227327542288151</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.6953368244083933</v>
+        <v>-0.7017257073438472</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8175178786021959</v>
+        <v>-0.8045387362037317</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.759419573606344</v>
+        <v>-0.7658358623250336</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.05593338141626</v>
+        <v>-1.062210352871929</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.951658191322799</v>
+        <v>-1.957626106026453</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.202235091909351</v>
+        <v>-2.189054082614113</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.479841476286602</v>
+        <v>-2.466642737331838</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.624750452462784</v>
+        <v>-2.63064095604436</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.376668192055178</v>
+        <v>-2.38267703561619</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.539646171643589</v>
+        <v>-2.54559575176998</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.217419085926487</v>
+        <v>-2.223540254849098</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.599000880354076</v>
+        <v>-2.592733318487909</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 65.99</t>
+          <t>X &lt; 65.98</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.096980554542398</v>
+        <v>-1.101957910003193</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9533935345370992</v>
+        <v>-0.9585871372221604</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7848158817612756</v>
+        <v>-0.7901103056274934</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.7726278481111564</v>
+        <v>-0.7779162584253925</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8493856935861004</v>
+        <v>-0.854706073332764</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9429165763997318</v>
+        <v>-0.9481778036415633</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.657797839676064</v>
+        <v>-1.662826959876483</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.988462467126517</v>
+        <v>-1.975281457831279</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.254240510305408</v>
+        <v>-2.241041771350645</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.335171675778376</v>
+        <v>-2.340107325359675</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.248347651292676</v>
+        <v>-2.253336945033737</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.332163996972596</v>
+        <v>-2.337124227085063</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.084642854280517</v>
+        <v>-2.089733760745936</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.260706263578449</v>
+        <v>-2.255467357292268</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 68.71</t>
+          <t>X &lt; 68.7</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.148219519561678</v>
+        <v>-1.152335343560928</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9597460447176829</v>
+        <v>-0.9640632257051536</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8508374999719166</v>
+        <v>-0.8552262969394704</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7680700769232232</v>
+        <v>-0.7724771030068283</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8996099036700969</v>
+        <v>-0.9040229275944967</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7469704208834642</v>
+        <v>-0.751410042071619</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.366337578765155</v>
+        <v>-1.370585935803327</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.671130591057533</v>
+        <v>-1.657949581762296</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.959477018324606</v>
+        <v>-1.946278279369842</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.175013494200996</v>
+        <v>-2.179113607041039</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.102256699741325</v>
+        <v>-2.106400492969499</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.375358540576535</v>
+        <v>-2.379413128878902</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.16020870905048</v>
+        <v>-2.164371799578163</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.185534850736246</v>
+        <v>-2.181079614098358</v>
       </c>
     </row>
     <row r="27">
@@ -5003,46 +5003,46 @@
         <v>3242</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.094729436102995</v>
+        <v>-1.112948001023128</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.183732720382103</v>
+        <v>-1.201573218309122</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.316244835402934</v>
+        <v>-1.333997470211116</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9542428917787049</v>
+        <v>-0.9720329801494714</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.076100430453408</v>
+        <v>-1.093768327217283</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.039178213091262</v>
+        <v>-1.056923494136797</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.569378074936552</v>
+        <v>-1.587109480013957</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.974966154962274</v>
+        <v>-1.97620672368749</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.220751997411909</v>
+        <v>-2.222031763759247</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.284369859029674</v>
+        <v>-2.301771878635016</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.318463929383391</v>
+        <v>-2.335823276659305</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.575708411259072</v>
+        <v>-2.593082263106162</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.177687255713849</v>
+        <v>-2.194966855369017</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.157920708602887</v>
+        <v>-2.168350344301039</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.095145709082516</v>
+        <v>-1.097749461964604</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.219263994422761</v>
+        <v>-1.22192255338917</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.421824675116916</v>
+        <v>-1.424447124372065</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.217005232561085</v>
+        <v>-1.219682238108007</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.120839762612732</v>
+        <v>-1.123576692168157</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.161314331689645</v>
+        <v>-1.164024247789278</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.554674031724289</v>
+        <v>-1.557274247491634</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.874408300455656</v>
+        <v>-1.861227291160418</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.935408186637957</v>
+        <v>-1.922209447683194</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.12084661190184</v>
+        <v>-2.123352071792461</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.04411489568831</v>
+        <v>-2.046655916845481</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.229851488224703</v>
+        <v>-2.232337283792148</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.807468317164719</v>
+        <v>-1.81010377182627</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.836879647194245</v>
+        <v>-1.833898498354529</v>
       </c>
     </row>
     <row r="29">
@@ -5104,153 +5104,153 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.8267716535433038</v>
+        <v>-0.8279067058663685</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7566084293595949</v>
+        <v>-0.7851490427615531</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8537528839765827</v>
+        <v>-0.8538511730408089</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7648777192074263</v>
+        <v>-0.7932999484752656</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5528451023259962</v>
+        <v>-0.580935089006239</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6643550164858851</v>
+        <v>-0.6926402889045775</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9601961893982178</v>
+        <v>-0.9885295545960844</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.298951865475956</v>
+        <v>-1.298833265004305</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.416560865725621</v>
+        <v>-1.40120581812117</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.656887929881236</v>
+        <v>-1.656392244017724</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.534703627169101</v>
+        <v>-1.534066815422364</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.824755682665341</v>
+        <v>-1.82421944283837</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.549510360638827</v>
+        <v>-1.548676887022765</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.567613641914399</v>
+        <v>-1.562492685388129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 79.58</t>
+          <t>X &lt; 79.57</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4584751953806929</v>
+        <v>-0.4601623440242477</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.307197725523956</v>
+        <v>-0.3089827573048183</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.4413947146546704</v>
+        <v>-0.4431576613586898</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4057127996728909</v>
+        <v>-0.4074819258471152</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2731020446309032</v>
+        <v>-0.2749269829234251</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4257052527911611</v>
+        <v>-0.427479119289174</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6324130052120864</v>
+        <v>-0.6341342037279531</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9753317823470056</v>
+        <v>-0.9769762702113383</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9941232940102296</v>
+        <v>-0.9957656608279635</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.281754119648028</v>
+        <v>-1.283348141968396</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.224992271450631</v>
+        <v>-1.226609843574117</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.531690371632699</v>
+        <v>-1.533223656390305</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.306641521693223</v>
+        <v>-1.308251949924632</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.315868206898287</v>
+        <v>-1.313992740982442</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 82.3</t>
+          <t>X &lt; 82.29</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3773</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1954985420800242</v>
+        <v>-0.1829762524044014</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1816301630289274</v>
+        <v>-0.1687203534528763</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2979778913564459</v>
+        <v>-0.2849707599388438</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1533970022730244</v>
+        <v>-0.1404178598745602</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1486621542820288</v>
+        <v>-0.1355513499070895</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.207009852491268</v>
+        <v>-0.1939669561969026</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3831711896228001</v>
+        <v>-0.370104935322324</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.6507482985624975</v>
+        <v>-0.6375672892672597</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5385052584340499</v>
+        <v>-0.5253065194792867</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9240593503912038</v>
+        <v>-0.9106542227383727</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.8758599232200623</v>
+        <v>-0.8624026295098446</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.197661522861949</v>
+        <v>-1.184209234141839</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.099885832371797</v>
+        <v>-1.086329786020194</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.9149499790466535</v>
+        <v>-0.8988755066080429</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3875</v>
+        <v>3876</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2043436700042136</v>
+        <v>-0.2052667633705596</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07877061596300905</v>
+        <v>-0.07975644458583986</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2538693170739563</v>
+        <v>-0.2548179385050062</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2898334273692456</v>
+        <v>-0.2907708557581685</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2221578880439381</v>
+        <v>-0.223123246045887</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2454252238708534</v>
+        <v>-0.2463795421904464</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2903945976190059</v>
+        <v>-0.2913394032989913</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3570613909111486</v>
+        <v>-0.3579982235813119</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3266165702610593</v>
+        <v>-0.3275628731039077</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.543873256393276</v>
+        <v>-0.54477992660523</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.5022290109028589</v>
+        <v>-0.5031507255157166</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.8403565130144344</v>
+        <v>-0.8411908830425858</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.807720602126075</v>
+        <v>-0.8085717141824063</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7242298367794433</v>
+        <v>-0.7232276671578433</v>
       </c>
     </row>
     <row r="33">
@@ -5312,153 +5312,153 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3958</v>
+        <v>3959</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2144154040679496</v>
+        <v>-0.2150550033440197</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1251630666754977</v>
+        <v>-0.1258467723012799</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2292835120308396</v>
+        <v>-0.2299465562121625</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3625710555504256</v>
+        <v>-0.363199133220391</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3580109102869216</v>
+        <v>-0.3586475952799049</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.4250293765521107</v>
+        <v>-0.4256455620343971</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.470876441262476</v>
+        <v>-0.4714825177891697</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5207479167189177</v>
+        <v>-0.5213479354145605</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4670261839297751</v>
+        <v>-0.4676408903843949</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6975762812235189</v>
+        <v>-0.6981444244994179</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.711626229451582</v>
+        <v>-0.7121938666011971</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.9409888357256904</v>
+        <v>-0.9414984329694747</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.9936498547779351</v>
+        <v>-0.9941520467836256</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.9572507499157581</v>
+        <v>-0.9564293883084005</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 90.45</t>
+          <t>X &lt; 90.44</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4018</v>
+        <v>4019</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.07468366875872334</v>
+        <v>-0.07516206228038413</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.01071912920401275</v>
+        <v>-0.01122889114965631</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1191410021436141</v>
+        <v>-0.1196278507849797</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2981280036876512</v>
+        <v>-0.2985694369912153</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3016419678277487</v>
+        <v>-0.3020878682081189</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2886991839237112</v>
+        <v>-0.2891457109222557</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4344709365747121</v>
+        <v>-0.4348822951816445</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4160030258221212</v>
+        <v>-0.4164236366199887</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4136803863084921</v>
+        <v>-0.4141023837852487</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5540070026142772</v>
+        <v>-0.5544024322493257</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5211279862282581</v>
+        <v>-0.5215337642012443</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6967554571639454</v>
+        <v>-0.6971174593370506</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.754843543181849</v>
+        <v>-0.7551953152895834</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.7151995055281333</v>
+        <v>-0.7146063377706753</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 93.17</t>
+          <t>X &lt; 93.16</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1136482298999866</v>
+        <v>-0.1139077338042398</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.0209646293257677</v>
+        <v>0.0206633145272761</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.09206623195641583</v>
+        <v>-0.09234225835322007</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1683573557221862</v>
+        <v>-0.1686141767306708</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1804650427827639</v>
+        <v>-0.1807219921155578</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2117798050476978</v>
+        <v>-0.2120276067693183</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3076602280204099</v>
+        <v>-0.3078851956832338</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2725483504513591</v>
+        <v>-0.2727845925739061</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2467568510748137</v>
+        <v>-0.2469998644270675</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2517311635646635</v>
+        <v>-0.2519777644049128</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2715513051545102</v>
+        <v>-0.2717943174597011</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3458302009194725</v>
+        <v>-0.3460549831408386</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3607241780974633</v>
+        <v>-0.3609477571916813</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3420744546430186</v>
+        <v>-0.3417507189734224</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/rsi/rsi_10.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_10.xlsx
@@ -568,53 +568,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 15.71</t>
+          <t>X ≈ 15.72</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>50</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13.47577232800231</v>
+        <v>13.44678927690232</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.08590981126514</v>
+        <v>-2.08710976374973</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.497953085427561</v>
+        <v>5.497841754745608</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.619698321100024</v>
+        <v>9.61926872507982</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.084776914150716</v>
+        <v>9.133267705342618</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.384040171577055</v>
+        <v>9.407998577602072</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>15.2915115103586</v>
+        <v>15.33950867685301</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.843558033616084</v>
+        <v>4.892749997811961</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.206082630895175</v>
+        <v>-3.132930252160676</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.057992863822591</v>
+        <v>-1.958752586285428</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.260092616689022</v>
+        <v>-6.16027401465314</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.227421246598283</v>
+        <v>-6.103795847790913</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.649038009045604</v>
+        <v>-6.500390695700617</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.424982053121845</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="7">
@@ -624,153 +624,153 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.253027971620007</v>
+        <v>9.712586598406112</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.115684171535655</v>
+        <v>9.531630699125195</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.58993785677497</v>
+        <v>13.47201723669102</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17.65755646797131</v>
+        <v>19.39174650302698</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.19023773722163</v>
+        <v>14.556101013319</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.55558434832821</v>
+        <v>12.72913892531392</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.005940804156</v>
+        <v>11.22377481275372</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.073755384193305</v>
+        <v>9.306930516068114</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.015194400803445</v>
+        <v>9.268451778749757</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.760744681416703</v>
+        <v>4.09130400786232</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.851517510959212</v>
+        <v>-1.091491301826359</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.591755462314516</v>
+        <v>3.311850949141537</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.7021000582379742</v>
+        <v>1.468669006513416</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.9279591233471649</v>
+        <v>1.718031199198187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 21.14</t>
+          <t>X ≈ 21.15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.31930515873897</v>
+        <v>-3.750382342171029</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2277689375599579</v>
+        <v>0.9040244726049664</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.784098328403545</v>
+        <v>-8.218906160105618</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.193452956411001</v>
+        <v>-6.84387286419539</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5734738635619934</v>
+        <v>-1.095104830983608</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.419660075343998</v>
+        <v>2.920731785668679</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.103739032170495</v>
+        <v>1.612941633137652</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.4053891887219621</v>
+        <v>-0.1001629061759033</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.344950124787168</v>
+        <v>-0.1368245362850686</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.437159805490126</v>
+        <v>-5.956180631709017</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.409391924875031</v>
+        <v>-4.910973379206069</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.078180609760516</v>
+        <v>-8.602384315819769</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-10.96883017723178</v>
+        <v>-11.49903000850282</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.74596970744374</v>
+        <v>-11.25298329355723</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 23.86</t>
+          <t>X ≈ 23.87</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>90</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.385382154885455</v>
+        <v>5.782117840975843</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7568231685069122</v>
+        <v>-1.356347233033866</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.496577421652326</v>
+        <v>6.007953771231243</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.627935039154757</v>
+        <v>5.03192713030861</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.200610264262153</v>
+        <v>5.649879251469834</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.499253255749927</v>
+        <v>7.033978309389965</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.198456555168519</v>
+        <v>4.754798742261059</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.4053521518157197</v>
+        <v>0.9548931913566889</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.454587018313134</v>
+        <v>2.025393938299018</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5038253772267183</v>
+        <v>-0.4047891091852307</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4017873187759236</v>
+        <v>0.5016095105101854</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.895535091930192</v>
+        <v>-2.771913692232154</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.20557710829064</v>
+        <v>-2.056931876936673</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.6974277380000373</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.921840244305997</v>
+        <v>-3.82119041716593</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.825116884730079</v>
+        <v>-2.873686109670679</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.361898113331357</v>
+        <v>-3.270811920675094</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.091300727858588</v>
+        <v>-3.139466465458753</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.492987183381324</v>
+        <v>-4.488919136439563</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.0556325517475</v>
+        <v>-5.066134146817333</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.003643672515182</v>
+        <v>-5.984832941837809</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.616034152207149</v>
+        <v>-4.754367664051806</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.958520357990736</v>
+        <v>-3.470170499717902</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.540800509793613</v>
+        <v>-6.01108442819671</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.16544914732097</v>
+        <v>-3.6554511938049</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.85503029551284</v>
+        <v>-5.676231384530752</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-6.281324443698047</v>
+        <v>-6.072900989210019</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.70084412208827</v>
+        <v>-4.970932011504814</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>131</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.471588653168311</v>
+        <v>2.412937973677366</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9.237914636186531</v>
+        <v>8.428482655871292</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.9952473164496</v>
+        <v>2.697111568493987</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1584755297615885</v>
+        <v>0.5418087411375936</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.350783638943611</v>
+        <v>3.098726526954849</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3629631648186944</v>
+        <v>1.085904791056485</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2788300911759762</v>
+        <v>0.6747657552241293</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9495033549943983</v>
+        <v>-0.9011353673433504</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.010466560328339</v>
+        <v>-0.9379710653236017</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.004693881554026</v>
+        <v>5.105224897233583</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.327266174096174</v>
+        <v>6.427111877175165</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.836942110523403</v>
+        <v>4.959372885868397</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.181343365352831</v>
+        <v>5.328729854567214</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.643720236953584</v>
+        <v>4.815718996520069</v>
       </c>
     </row>
     <row r="12">
@@ -887,1190 +887,1190 @@
         <v>148</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.166760327163281</v>
+        <v>-4.882852185981847</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.059656216278881</v>
+        <v>-1.752008068883761</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.47480571354123</v>
+        <v>-4.173630202404055</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.345892379739212</v>
+        <v>-4.044433354768621</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.84007255013735</v>
+        <v>-0.7921711612343145</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.91449633164811</v>
+        <v>-3.895866588399194</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.301894596050488</v>
+        <v>-1.255272097223411</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.792333802093559</v>
+        <v>-3.746549115800768</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.154602631854878</v>
+        <v>-1.082254688632496</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.679160976598524</v>
+        <v>-2.580803502019457</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.88462135310445</v>
+        <v>-2.784795846423116</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.526696200938048</v>
+        <v>-3.401925298255485</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.623690676322106</v>
+        <v>-4.473537047394693</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.749306377447077</v>
+        <v>-5.577307617880265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 34.73</t>
+          <t>X ≈ 34.72</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>163</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2781190941667191</v>
+        <v>0.2499806336183852</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.729186781369897</v>
+        <v>1.732427487407897</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.559842796391059</v>
+        <v>2.565623654947743</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.467204094682529</v>
+        <v>1.470078796399306</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.153769275986761</v>
+        <v>2.207158600365133</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.221051675781069</v>
+        <v>-1.198772256464842</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.918202545984535</v>
+        <v>-1.87247561920406</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.5469261897208426</v>
+        <v>-0.4984633653751658</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.004795242032415103</v>
+        <v>0.07777357446435218</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2313266513772163</v>
+        <v>-0.1323045391656379</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.727932013976314</v>
+        <v>-4.628118482829521</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.015338388775085</v>
+        <v>-0.891235369816016</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8224968444534397</v>
+        <v>-0.673373029189861</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.210258126742382</v>
+        <v>-1.038259367175719</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 37.45</t>
+          <t>X ≈ 37.44</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.469701062178473</v>
+        <v>-4.626767728489973</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.866471566887718</v>
+        <v>2.809065944674693</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.665087683459198</v>
+        <v>3.015986578638625</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.393476007334066</v>
+        <v>4.073796584550657</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.258504258259201</v>
+        <v>2.380569364265767</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.153634346710163</v>
+        <v>3.255493578543089</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.862729344550822</v>
+        <v>4.398975201495055</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.59963873753113</v>
+        <v>2.729583397995363</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.538713693639146</v>
+        <v>2.692690605280667</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.077474153941921</v>
+        <v>4.277616347354396</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.667021504410116</v>
+        <v>5.879852077982051</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.697989128467022</v>
+        <v>8.947993944838437</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.816348164914189</v>
+        <v>9.76012740854484</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>6.449269443883232</v>
+        <v>6.397619116082318</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 40.17</t>
+          <t>X ≈ 40.16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.589694345943684</v>
+        <v>1.874430935998362</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.315549562440566</v>
+        <v>0.2865168601180343</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.55774696201113</v>
+        <v>1.147896159692728</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.053434330913163</v>
+        <v>0.02073429956236339</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.296509372945053</v>
+        <v>-3.613057337938379</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.270898706106856</v>
+        <v>-4.598667140695071</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.356830752824955</v>
+        <v>-4.031185827885132</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-6.096203145472707</v>
+        <v>-6.388177895525565</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7.431744437881733</v>
+        <v>-7.683353051919354</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-6.374088696325295</v>
+        <v>-6.626817687319011</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-10.40130701703636</v>
+        <v>-9.977042825953127</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.91846493920785</v>
+        <v>-12.4316184710479</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-8.880017066406758</v>
+        <v>-8.700198116035118</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.832625365224523</v>
+        <v>-4.680656249530792</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 42.89</t>
+          <t>X ≈ 42.87</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>178</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.35256966887497</v>
+        <v>-1.385056601264608</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.199026952332567</v>
+        <v>-5.213539908215651</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5544518201614395</v>
+        <v>-0.5544673975170724</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.256324673073152</v>
+        <v>1.260196139102739</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.082240531370651</v>
+        <v>-2.036894283728302</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.784829918094857</v>
+        <v>-1.764021584251878</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.991550180748249</v>
+        <v>-2.947839094988105</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.214294820741266</v>
+        <v>-1.166938017823192</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.959193340760962</v>
+        <v>-2.888615396087019</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-6.055283929261279</v>
+        <v>-5.958480369192635</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.76949147126826</v>
+        <v>-1.669651316815653</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.104317081188206</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.718133433686369</v>
+        <v>-2.568210762390699</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.739588794695919</v>
+        <v>-4.567590035129122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 45.6</t>
+          <t>X ≈ 45.59</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3959013640814746</v>
+        <v>0.1213682892349794</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.9646514171960447</v>
+        <v>-0.4090130445746922</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.473196253050851</v>
+        <v>-3.959406787896242</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8472390567509365</v>
+        <v>1.431533267103354</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.349866397117907</v>
+        <v>1.468607714255697</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.727059615442784</v>
+        <v>3.845932468075681</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.683746778702115</v>
+        <v>4.837553120100125</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.619856366189879</v>
+        <v>1.741527169037305</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.12035284096762</v>
+        <v>3.28301241427031</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1905272131197506</v>
+        <v>0.3551860033942447</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.01440754473273387</v>
+        <v>0.151188030842512</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5014001833692134</v>
+        <v>-0.3167408599222412</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.203448963317264</v>
+        <v>2.444788962279269</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6958153864560899</v>
+        <v>0.06280618012811345</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 48.32</t>
+          <t>X ≈ 48.3</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.772343552454046</v>
+        <v>-3.327389758166646</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.482151109337266</v>
+        <v>-5.992904492954871</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.79241448232812</v>
+        <v>-5.022701131588931</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.634824724484389</v>
+        <v>-8.117477044411913</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-10.90291722481253</v>
+        <v>-10.75612530987195</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.612101238716967</v>
+        <v>-4.571807122421994</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.671977546962083</v>
+        <v>-7.856875547769796</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.049117861692132</v>
+        <v>-7.247397955040569</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-11.47900461995159</v>
+        <v>-11.58353198613678</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.965010080161136</v>
+        <v>-8.107522322689363</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-7.627217997503323</v>
+        <v>-7.774090132974543</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.864446631456644</v>
+        <v>-5.028852586683854</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.738149397338233</v>
+        <v>-4.886668986051014</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.151758009406905</v>
+        <v>-6.790617702158244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 51.04</t>
+          <t>X ≈ 51.02</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>218</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.785665864540526</v>
+        <v>-4.126426776200937</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.118800804473921</v>
+        <v>-3.883286200330353</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7655737250460746</v>
+        <v>-0.149745126979866</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.848283438113448</v>
+        <v>-2.770799807555171</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.729697601838112</v>
+        <v>0.8649075025440425</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.944402395665932</v>
+        <v>2.056672621099658</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.382723783542104</v>
+        <v>-6.262412609146999</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.107858788259499</v>
+        <v>-3.981371216315445</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.547909179312398</v>
+        <v>-5.397200326826393</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.571513770767751</v>
+        <v>-4.391392396202654</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.028362724893498</v>
+        <v>-1.84498122371771</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7259796940724712</v>
+        <v>-1.786233833699377</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.063561740046431</v>
+        <v>-2.639139602170779</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.75525728248045</v>
+        <v>-3.500689715574445</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 53.75</t>
+          <t>X ≈ 53.73</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.547804001703604</v>
+        <v>-4.838867407321459</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.962487732714564</v>
+        <v>-1.243547977400475</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.1998797182427765</v>
+        <v>0.4352528943885687</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.78545681401333</v>
+        <v>-2.543671354552195</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.765549591629444</v>
+        <v>-1.47851635042651</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.029255212109362</v>
+        <v>-2.760134976685187</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.710326286638363</v>
+        <v>-4.893329926014381</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.538943788411274</v>
+        <v>-1.732219681216264</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.601162630170997</v>
+        <v>-1.769192290353061</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.932448203991477</v>
+        <v>-2.074886156142135</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.619111669057986</v>
+        <v>-1.760891888652203</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-4.147233516702784</v>
+        <v>-3.257129296364916</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.525717703349407</v>
+        <v>-3.134152507903295</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.174982053122875</v>
+        <v>0.7418353592936526</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 56.47</t>
+          <t>X ≈ 56.45</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.452023228891342</v>
+        <v>0.8609173501238558</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.232358644179875</v>
+        <v>-4.655086662851758</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.062736312175559</v>
+        <v>-5.048824651166406</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.933232494817545</v>
+        <v>-4.918940609951854</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.34820827112835</v>
+        <v>-4.284594245285788</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.436149905678057</v>
+        <v>-7.382595243320985</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.655162658181254</v>
+        <v>-9.128644590973096</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-9.367554396318546</v>
+        <v>-10.15627510416556</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.354855425245667</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.772779733730083</v>
+        <v>-6.522694271645427</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.462685115385291</v>
+        <v>-2.232452696709863</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.123222217267383</v>
+        <v>-3.859679217771806</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.108344821993349</v>
+        <v>-4.816634897144489</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.447580923179252</v>
+        <v>-5.129387787938114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 59.19</t>
+          <t>X ≈ 59.17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.66821649587343</v>
+        <v>1.901294218433769</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9387906490125886</v>
+        <v>-0.6619163610232874</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8383251896956025</v>
+        <v>-0.5654582709066176</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.202000049259553</v>
+        <v>-0.9257703081232549</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.72775223268593</v>
+        <v>-1.905215527506542</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.617376469009592</v>
+        <v>-4.083410400844372</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.740924096873933</v>
+        <v>-2.673478254775816</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.703262232671911</v>
+        <v>-3.629507093590419</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.278307104990944</v>
+        <v>-3.176283624295955</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.676007390928994</v>
+        <v>-1.549131812953974</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.062974559041557</v>
+        <v>-3.22386049578418</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.02859640668612</v>
+        <v>-3.165693758419394</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.926579772314803</v>
+        <v>-5.031439920277222</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.178676634403537</v>
+        <v>-6.252983293556149</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.91</t>
+          <t>X ≈ 61.88</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-5.442758137949141</v>
+        <v>-4.899301095204081</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.671706931991892</v>
+        <v>-0.2471350638889902</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.851900829911074</v>
+        <v>-6.558032815517173</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.344990214271689</v>
+        <v>-4.061284868977182</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.886567123336334</v>
+        <v>-5.14224998626046</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.183221894621191</v>
+        <v>-5.461180443773024</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.076526334238117</v>
+        <v>-3.74668860400427</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.164493436839784</v>
+        <v>-1.845657459062096</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.419086352936525</v>
+        <v>-3.066062020861686</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.084053367940534</v>
+        <v>-2.706458649013946</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.693516430962632</v>
+        <v>-2.318883120218679</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.254376373845403</v>
+        <v>-2.852432359185144</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.484051036682622</v>
+        <v>-2.064158333086255</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.44879157693228</v>
+        <v>-2.998545423733468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 64.62</t>
+          <t>X ≈ 64.59</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>160</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.190009516855199</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.054790001711012</v>
+        <v>-5.343288910042837</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.330570129832033</v>
+        <v>-3.237026898357612</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3290161431329111</v>
+        <v>-1.232142857142861</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.388377869839388</v>
+        <v>-3.596391998094788</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.029547761219348</v>
+        <v>-0.1986064792757816</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.443908419117847</v>
+        <v>2.86573743149868</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.730334179996106</v>
+        <v>1.14990467111528</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.66756489228726</v>
+        <v>0.4879320619785474</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.689756155868992</v>
+        <v>1.539103481163558</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>-1.165036966372519</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.269433149964115</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2242822966507134</v>
+        <v>-0.877028155571459</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>2.49701670644383</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 67.34</t>
+          <t>X ≈ 67.31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.136650613406111</v>
+        <v>-2.510111824886906</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.065386924979826</v>
+        <v>-0.7599555767095012</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.130367682964753</v>
+        <v>-1.820360231690948</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6604566513575634</v>
+        <v>-0.357142857142783</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.867343289112789</v>
+        <v>-1.513058664761445</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.119444349496938</v>
+        <v>3.426393520724076</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.377937598766636</v>
+        <v>4.032404098165351</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.582983760156537</v>
+        <v>4.23323800444868</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.851787292652752</v>
+        <v>4.196265395311883</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.9867360216408017</v>
+        <v>1.372436814496901</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7820348633806091</v>
+        <v>1.16829636696081</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.210432621847957</v>
+        <v>-2.773536895674297</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.630583475161366</v>
+        <v>-3.168694822238123</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.7202840665455739</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 70.06</t>
+          <t>X ≈ 70.03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3772446401980574</v>
+        <v>-0.07108743464314671</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.570563882754087</v>
+        <v>-6.532313300286738</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-10.14812452936788</v>
+        <v>-10.58458787396723</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.640869312606185</v>
+        <v>-5.576655052264812</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.579681322238557</v>
+        <v>-5.456148095655756</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.673735337490271</v>
+        <v>-7.012630869519754</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.559294181679036</v>
+        <v>-5.244018666062289</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.816152617233591</v>
+        <v>-8.758631914250444</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7.291819828669254</v>
+        <v>-8.185848425826336</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-4.56323785610698</v>
+        <v>-5.351140421275524</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-6.564346199996059</v>
+        <v>-7.384549161494547</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.529968047640736</v>
+        <v>-7.326382424129584</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.758502134487074</v>
+        <v>-3.453247667766512</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.933964089050832</v>
+        <v>-2.594446708190233</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 72.78</t>
+          <t>X ≈ 72.74</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.7448377976005176</v>
+        <v>-0.4830847978599238</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.66236147339422</v>
+        <v>-0.03923485598878074</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.431276962916513</v>
+        <v>-2.45999987133051</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.743826241743257</v>
+        <v>-5.032818532818617</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.776477624051417</v>
+        <v>-0.1166622683650544</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.543614934010286</v>
+        <v>-2.54657945224875</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8715245290971652</v>
+        <v>-0.5802085144472571</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.7297625462272421</v>
+        <v>2.332337103547701</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.794244027814294</v>
+        <v>6.349418548465039</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.870790638627447</v>
+        <v>3.498562940623103</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.424710170022749</v>
+        <v>5.997125195789792</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.838398667205581</v>
+        <v>7.406643284505876</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.79755815871976</v>
+        <v>8.362836709293326</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.643983464118548</v>
+        <v>7.26053021995746</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 75.5</t>
+          <t>X ≈ 75.45</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.680051033474086</v>
+        <v>5.04384500964531</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>9.760037877036545</v>
+        <v>9.216063607942772</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>12.92545039699211</v>
+        <v>12.41944792178634</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.494780342687939</v>
+        <v>8.952209660842747</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12.52165374657685</v>
+        <v>12.0600828220491</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>10.67950322611193</v>
+        <v>10.89401942000472</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12.72364801921559</v>
+        <v>12.99163671207423</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>12.24662127088053</v>
+        <v>12.52580395169088</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>11.21484285159852</v>
+        <v>11.04998242169078</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.654041870154785</v>
+        <v>9.506729380444099</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.87791214046585</v>
+        <v>10.74143785377127</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.055147435678414</v>
+        <v>7.921906749409679</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.777853725222144</v>
+        <v>4.649050981119153</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.003589375448676</v>
+        <v>4.89809584313452</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 78.22</t>
+          <t>X ≈ 78.17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>10.16600031956633</v>
+        <v>9.156554841779773</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>13.45754986630573</v>
+        <v>14.24004442329045</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.41960993248505</v>
+        <v>11.34630643497574</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.73271246943961</v>
+        <v>12.30952380952375</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.560177703076121</v>
+        <v>9.320274668571933</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.214383183645609</v>
+        <v>8.759726854057533</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.573392070740013</v>
+        <v>9.532404098165401</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.268804624210027</v>
+        <v>9.066571337782015</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.66046504984567</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.513526647672322</v>
+        <v>9.872436814496936</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.669481227117004</v>
+        <v>8.001629700294146</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.884187248324778</v>
+        <v>6.393129770992324</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.644364263863828</v>
+        <v>5.164638511095255</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.87009991409036</v>
+        <v>5.41368337311058</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 80.93</t>
+          <t>X ≈ 80.89</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.002954937207626</v>
+        <v>9.028349713574514</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.972414005434104</v>
+        <v>3.599018782264913</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.384094233582267</v>
+        <v>4.743742332411735</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.740125828783484</v>
+        <v>6.412087912087948</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.976029824074935</v>
+        <v>3.615146463443637</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.692758692419766</v>
+        <v>4.65716275149336</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.41449994605675</v>
+        <v>6.904198969960184</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.366786140979691</v>
+        <v>7.976827748038417</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>13.33806204897304</v>
+        <v>11.78600898505547</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.06878841393346</v>
+        <v>8.654488096548178</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>9.864087255673311</v>
+        <v>8.450347649012087</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.092013795125403</v>
+        <v>8.50851438637698</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.446056490199098</v>
+        <v>5.036433382890081</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.31695343074821</v>
+        <v>10.67009362952083</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 83.65</t>
+          <t>X ≈ 83.6</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.024605350922705</v>
+        <v>-0.5101118248869838</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.189451274460048</v>
+        <v>3.906711089957106</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.8529323168894933</v>
+        <v>0.5129731016424657</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-5.812959044376505</v>
+        <v>-6.357142857142861</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.438627238248905</v>
+        <v>-3.846391998094781</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.170379422206068</v>
+        <v>-2.573606479275881</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.599279150566616</v>
+        <v>2.36573743149868</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.899200798042024</v>
+        <v>9.899904671115344</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.925597282295932</v>
+        <v>6.862932061978547</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.87179499082045</v>
+        <v>12.03910348116359</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.66709383256025</v>
+        <v>11.8349630336275</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.73059819850781</v>
+        <v>10.89312977099237</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.368699772378875</v>
+        <v>8.497971844428541</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.710940276974362</v>
+        <v>4.747016706443908</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 86.37</t>
+          <t>X ≈ 86.32</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>83</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.6736871148717043</v>
+        <v>-3.112521463441219</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.284873207935554</v>
+        <v>-4.695698548597015</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.9348132386347316</v>
+        <v>-0.2701594284780242</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.754238726210644</v>
+        <v>-4.959552495697082</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.702166833523201</v>
+        <v>-6.653620913757429</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-8.814431358105018</v>
+        <v>-8.790473949155334</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.899141717371116</v>
+        <v>-8.85113003838083</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.161391084049455</v>
+        <v>-8.112143521655774</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.017553963463769</v>
+        <v>-6.944296853684072</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-7.867472759793628</v>
+        <v>-6.563306157390684</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.48181247227072</v>
+        <v>-9.17708515914368</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-5.6281572114817</v>
+        <v>-4.299641313345013</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.662765896120369</v>
+        <v>-8.309257071234107</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-11.84666880011077</v>
+        <v>-10.46985076343561</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 89.09</t>
+          <t>X ≈ 89.03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.185750636132319</v>
+        <v>11.42431440462124</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.574564543068512</v>
+        <v>9.841137319465368</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.179793158313451</v>
+        <v>9.447399331150663</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>6.298594847775171</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.438395415472804</v>
+        <v>4.170001444528168</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.735769445107941</v>
+        <v>9.360819750232295</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.984392419174966</v>
+        <v>2.742786611826553</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.517323775388277</v>
+        <v>7.194986638328508</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.12300828553213</v>
+        <v>5.518669766896537</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.939756155868949</v>
+        <v>11.25221823526195</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.06838833094213</v>
+        <v>14.32676631231604</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.43609981663085</v>
+        <v>17.6636215742711</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.0159489633174</v>
+        <v>17.26846364770723</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>15.24168461354396</v>
+        <v>17.51750850972258</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 91.8</t>
+          <t>X ≈ 91.75</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.968503937007874</v>
+        <v>1.789064031133634</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.573732552252849</v>
+        <v>1.395326042818944</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.764563756447266</v>
+        <v>7.407563025210081</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.226274203351558</v>
+        <v>6.918313884258176</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.493345202683606</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.438937873720512</v>
+        <v>7.130443313851629</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.487020745085282</v>
+        <v>8.135198788762402</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.941190103714007</v>
+        <v>8.098226179625605</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.18218039829324</v>
+        <v>16.0979270105753</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.94717620973002</v>
+        <v>12.952610092451</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.04216042269135</v>
+        <v>18.89312977099234</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>23.652312599681</v>
+        <v>21.43914831501677</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>22.36289673475601</v>
+        <v>20.21760494173802</v>
       </c>
     </row>
   </sheetData>
@@ -2210,209 +2210,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 14.35</t>
+          <t>X &gt; 14.36</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4085</v>
+        <v>4096</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.03250515052958036</v>
+        <v>0.03308603347272054</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.003744788963082613</v>
+        <v>-0.003707605271664249</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.06792819585322007</v>
+        <v>-0.0677427493436582</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07558606746957253</v>
+        <v>0.07539489249181486</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.009740067347607351</v>
+        <v>-0.01082561563436713</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1055878342275065</v>
+        <v>0.1047560938235605</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1808733575914516</v>
+        <v>0.1792884916985358</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.06943002487904693</v>
+        <v>0.0681153000768191</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2175478128345461</v>
+        <v>0.215285146592052</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.212683521973176</v>
+        <v>0.2098351884806462</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.266366152207631</v>
+        <v>0.2633602036689524</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1188336882562737</v>
+        <v>0.115677355179777</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1285285032097008</v>
+        <v>0.1247719420609528</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1233655600963388</v>
+        <v>0.1435010814439082</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 17.07</t>
+          <t>X &gt; 17.08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4035</v>
+        <v>4046</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1340780858703283</v>
+        <v>-0.1326789596492475</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.02205651242850593</v>
+        <v>0.02203883761610825</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1368982241218788</v>
+        <v>-0.1365215988751629</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.04268050320737871</v>
+        <v>-0.04254719639335036</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1224354450613419</v>
+        <v>-0.1238272631995869</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.009386792009777878</v>
+        <v>-0.01021230068680268</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.006371229183862681</v>
+        <v>-0.00805975577000595</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.01027106566298386</v>
+        <v>0.008493022546730344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2599719819018276</v>
+        <v>0.2566620052024362</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2408207758244245</v>
+        <v>0.2366343453610966</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3472392472373258</v>
+        <v>0.3427427323185057</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1974737741900299</v>
+        <v>0.1925368856168816</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2125132183553688</v>
+        <v>0.2066449356071942</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2045098923543165</v>
+        <v>0.2225480954701098</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 19.78</t>
+          <t>X &gt; 19.79</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3967</v>
+        <v>3977</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2949863822931533</v>
+        <v>-0.3034919653082468</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1338211484788019</v>
+        <v>-0.1429503095913702</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3893370578755935</v>
+        <v>-0.372626496952627</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3460876406009135</v>
+        <v>-0.379727549740096</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3677749399933461</v>
+        <v>-0.378520512151006</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2076267813072263</v>
+        <v>-0.2312370013642067</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1779964417543454</v>
+        <v>-0.2029294025460047</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1279484789954637</v>
+        <v>-0.152832646815348</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1270364829138515</v>
+        <v>0.1003096053093699</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1976257101374372</v>
+        <v>0.1697567474952208</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3849290530244147</v>
+        <v>0.3676263502103865</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1564323941062256</v>
+        <v>0.1384175317362661</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2041210063281369</v>
+        <v>0.1847491194411077</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1921089476334856</v>
+        <v>0.1966018208517468</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 22.5</t>
+          <t>X &gt; 22.51</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3886</v>
+        <v>3897</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2111032580285794</v>
+        <v>-0.2327320910077546</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1413581523308665</v>
+        <v>-0.1644432484098743</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.214356187337053</v>
+        <v>-0.2115532680452006</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2242048329373461</v>
+        <v>-0.2470276202670618</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3634873401968761</v>
+        <v>-0.3638100308816661</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.283234150166912</v>
+        <v>-0.2959425448496162</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2255570628011583</v>
+        <v>-0.2402067140303927</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1390653989864887</v>
+        <v>-0.1539138834720433</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1224942788500982</v>
+        <v>0.1051776400354498</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3150774926299249</v>
+        <v>0.2955137375738275</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4848621459759954</v>
+        <v>0.4759886746531166</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3280751252727683</v>
+        <v>0.3178540592714185</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4370106218372314</v>
+        <v>0.4246008849621461</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.4201028671037008</v>
+        <v>0.4316459083941311</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3796</v>
+        <v>3807</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3675004358900864</v>
+        <v>-0.3749271248607897</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1267659891444026</v>
+        <v>-0.1362658492461861</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3497576691097208</v>
+        <v>-0.3585865313850647</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3629541976602937</v>
+        <v>-0.3718256049142354</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.5191166300813137</v>
+        <v>-0.5059776262091233</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4440412804441891</v>
+        <v>-0.4692267258009011</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3304467428899969</v>
+        <v>-0.3582919494037213</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.151973085912779</v>
+        <v>-0.1801268166831349</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.09091146890498436</v>
+        <v>0.05978245567933982</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3344929979742588</v>
+        <v>0.3120693604286586</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4868317809728353</v>
+        <v>0.4753829811340324</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4045042400115193</v>
+        <v>0.3908982141533031</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4996641770826358</v>
+        <v>0.483265962075599</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4506765348645985</v>
+        <v>0.4583379567722474</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3680</v>
+        <v>3690</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2869832027987087</v>
+        <v>-0.2656553619340372</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.0417092761313711</v>
+        <v>-0.04946959708638587</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.286331502933173</v>
+        <v>-0.2662476775783134</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2769519700779526</v>
+        <v>-0.2840711386042898</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3938533191620763</v>
+        <v>-0.3796892368603508</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2986759034139723</v>
+        <v>-0.3234711246467299</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1516177092387778</v>
+        <v>-0.1798894301314178</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.02026362161171846</v>
+        <v>-0.03508991176656195</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2185566025788717</v>
+        <v>0.1717077932894924</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5512142063712986</v>
+        <v>0.5125596025070109</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.6334797667560039</v>
+        <v>0.6063606500955174</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6018156547182656</v>
+        <v>0.5832706160627907</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.7134127314333227</v>
+        <v>0.6911444263846462</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6130614251381132</v>
+        <v>0.6304855411322521</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3549</v>
+        <v>3559</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3888070723765296</v>
+        <v>-0.3642492722923123</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3842369550588529</v>
+        <v>-0.3615268449474343</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3705486980132306</v>
+        <v>-0.3753232778130595</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2813251494753715</v>
+        <v>-0.3144702013315168</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4951628264914234</v>
+        <v>-0.5077230848681609</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3230981964369306</v>
+        <v>-0.3753475632410286</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1675063150021856</v>
+        <v>-0.2113476569596173</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.05605947225567576</v>
+        <v>-0.003212430822316037</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2639220673128335</v>
+        <v>0.2125529549861227</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3868282279410593</v>
+        <v>0.34351235507539</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4233118266710321</v>
+        <v>0.3921099024845418</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.4454894879922904</v>
+        <v>0.4221946404110639</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5484933420156111</v>
+        <v>0.5204437545408993</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4642825284495231</v>
+        <v>0.4764350823922143</v>
       </c>
     </row>
     <row r="13">
@@ -2578,1193 +2578,1193 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3401</v>
+        <v>3411</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1808867307980435</v>
+        <v>-0.1681914501797195</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3113283838561003</v>
+        <v>-0.3011952057968657</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1919453347970759</v>
+        <v>-0.2105184039228618</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1044489512751241</v>
+        <v>-0.1526306977523006</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4801535236100349</v>
+        <v>-0.4953811571923481</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1668127145165386</v>
+        <v>-0.22259563837342</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1181415794552407</v>
+        <v>-0.1660527823893929</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2235285121273805</v>
+        <v>0.1592073373913436</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3256514573383598</v>
+        <v>0.2687334097664191</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5202496928842635</v>
+        <v>0.4703955995344984</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5672618738944308</v>
+        <v>0.5299527787197675</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6183455544320751</v>
+        <v>0.5881195160846602</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7735692710700022</v>
+        <v>0.7371277647099035</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7346768707231703</v>
+        <v>0.7391011391615905</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 36.09</t>
+          <t>X &gt; 36.08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3238</v>
+        <v>3248</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2039929536112766</v>
+        <v>-0.1891773029072752</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.414047337510155</v>
+        <v>-0.4032520096738281</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3304695674665226</v>
+        <v>-0.3498383409905728</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1835655190611334</v>
+        <v>-0.2340659340659457</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.612744448975775</v>
+        <v>-0.631007382710159</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.113742624743189</v>
+        <v>-0.1736064792758469</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.02752702184428557</v>
+        <v>-0.08041641465516136</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2623129829121993</v>
+        <v>0.1922123634230388</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3418032680532619</v>
+        <v>0.2783166773631578</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5580838325120041</v>
+        <v>0.5006419427020248</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8338204297075649</v>
+        <v>0.7888091874736318</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.7005847399610303</v>
+        <v>0.6623605402231405</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8539147858415674</v>
+        <v>0.8079133648963719</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.8325843458889821</v>
+        <v>0.8282974946212462</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 38.81</t>
+          <t>X &gt; 38.8</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3071</v>
+        <v>3082</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.08235457296986937</v>
+        <v>0.04983632806181504</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5380612277851355</v>
+        <v>-0.5762710818418597</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4933670148467257</v>
+        <v>-0.5311254716389939</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3780838957814225</v>
+        <v>-0.4660922734852733</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.768882037418706</v>
+        <v>-0.7932143067847974</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2914215417841248</v>
+        <v>-0.3583016803134669</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2934576024981368</v>
+        <v>-0.3216815049474917</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1352099542500866</v>
+        <v>0.05554669446165406</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2223359801754299</v>
+        <v>0.1482757714467766</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3667005099204061</v>
+        <v>0.2972098365461875</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.570992497608799</v>
+        <v>0.5145998689063305</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.2656884414001368</v>
+        <v>0.2160869694359491</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.3665405187282076</v>
+        <v>0.3257370082300355</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5271508026245613</v>
+        <v>0.5283275435626678</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 41.53</t>
+          <t>X &gt; 41.51</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2914</v>
+        <v>2923</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.05273545597894724</v>
+        <v>-0.04941462734767299</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6379297569771154</v>
+        <v>-0.6232034399573649</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6038765873816132</v>
+        <v>-0.6224578149102058</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4552109931016162</v>
+        <v>-0.4925737736955256</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6326989586000309</v>
+        <v>-0.6398256506255606</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.07701594301998682</v>
+        <v>-0.127642046991312</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.07453186996508521</v>
+        <v>-0.1198986834123872</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4709449771246454</v>
+        <v>0.4060606218677307</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.6347212326239458</v>
+        <v>0.5742863711440762</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7298796126591114</v>
+        <v>0.6738504031881902</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.162156198294902</v>
+        <v>1.085305030891497</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.9760220312269894</v>
+        <v>0.9040736834410623</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8647249871105629</v>
+        <v>0.8167132944969424</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.8159239180508848</v>
+        <v>0.8116763027490776</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 44.24</t>
+          <t>X &gt; 44.23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2736</v>
+        <v>2745</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.03182978155595606</v>
+        <v>0.03719530757299339</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3411917084488678</v>
+        <v>-0.325542277352632</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6070920875881924</v>
+        <v>-0.62686666529126</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5665609012080139</v>
+        <v>-0.6062324419935479</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.5383939878569137</v>
+        <v>-0.5492324933606199</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.03409183752216194</v>
+        <v>-0.02153073273543527</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1152449061019425</v>
+        <v>0.06347960192840674</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5805841160209013</v>
+        <v>0.5080619908531503</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8685358503368548</v>
+        <v>0.798838835467258</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.171312036073523</v>
+        <v>1.103925039794305</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.352884738200686</v>
+        <v>1.263950651981439</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.444871746455348</v>
+        <v>1.358533995318659</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.09782030834662</v>
+        <v>1.036209280699488</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.177357128163798</v>
+        <v>1.160495759267221</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 46.96</t>
+          <t>X &gt; 46.95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2544</v>
+        <v>2555</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.06411137745311635</v>
+        <v>0.03093586862357256</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2941381455245633</v>
+        <v>-0.3193350578723297</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3153106411381827</v>
+        <v>-0.3790456777002689</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.673262784827557</v>
+        <v>-0.7577688352336338</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6809042055908563</v>
+        <v>-0.6992871467645756</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2446227117548716</v>
+        <v>-0.3091307359268711</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.229547688056563</v>
+        <v>-0.2915395638064737</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5021484744987106</v>
+        <v>0.4163365959979686</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6985873982137747</v>
+        <v>0.6141057708987319</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.245333532145509</v>
+        <v>1.159604263636183</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.456076608610765</v>
+        <v>1.346700122829347</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.59176019398928</v>
+        <v>1.483114121540098</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.014376636273361</v>
+        <v>0.9314616722845628</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.318728638701145</v>
+        <v>1.242124338537842</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 49.68</t>
+          <t>X &gt; 49.66</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2361</v>
+        <v>2369</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2839636655399431</v>
+        <v>0.2946119203681832</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1079823002093363</v>
+        <v>0.1261203726575886</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.03170757272786773</v>
+        <v>-0.01445305869508928</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1336753917918898</v>
+        <v>-0.1799276672694461</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1113992177541476</v>
+        <v>0.09031686266471439</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.09389849554460739</v>
+        <v>0.0255496388676022</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3473115513249354</v>
+        <v>0.3024462922581819</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.087443578066242</v>
+        <v>1.018048131030959</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.642466830371447</v>
+        <v>1.571792821472222</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.959222935386549</v>
+        <v>1.887204746986349</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.160118503112606</v>
+        <v>2.062811134893295</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.09217774970999</v>
+        <v>1.994395593777178</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.460252224647327</v>
+        <v>1.388267203078328</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.897762546623113</v>
+        <v>1.87280817963935</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 52.4</t>
+          <t>X &gt; 52.38</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2143</v>
+        <v>2151</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7996795953381408</v>
+        <v>0.7426762792022359</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5379583696544898</v>
+        <v>0.5324665525327035</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.04294610025642953</v>
+        <v>-0.0007414497289914834</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.04074577204296048</v>
+        <v>0.08265258683668009</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.05322469625906479</v>
+        <v>0.0118134877257603</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1960734364322647</v>
+        <v>-0.1803010399453129</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9302082862764109</v>
+        <v>0.9677829917032454</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.514217220557605</v>
+        <v>1.524730333597915</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.272192434716331</v>
+        <v>2.278087803494124</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.521845708107797</v>
+        <v>2.523529329606156</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.484471703161759</v>
+        <v>2.458858896017063</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.378859188228233</v>
+        <v>2.377555619434958</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.818717667625975</v>
+        <v>1.796437674275118</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.371098208193153</v>
+        <v>2.417402573482498</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 55.11</t>
+          <t>X &gt; 55.09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1951</v>
+        <v>1958</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.325931184590836</v>
+        <v>1.292848869344766</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.685618877934786</v>
+        <v>0.7075282503248843</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.06684284918101469</v>
+        <v>-0.0437173988682602</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3188753960936026</v>
+        <v>0.3415292572595874</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1152870310147023</v>
+        <v>0.1587152542034858</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.08274301714538268</v>
+        <v>0.07399311214395965</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.583710407239828</v>
+        <v>1.545512712397567</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.913093137380784</v>
+        <v>1.845767796753755</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.751784527211647</v>
+        <v>2.677028078321754</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.058608614885379</v>
+        <v>2.976795003124757</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.986720810012699</v>
+        <v>2.874799601553924</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.021098962368022</v>
+        <v>2.932966338918817</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.34466927768608</v>
+        <v>2.282445797441824</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.621660694186318</v>
+        <v>2.58256318243982</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 57.83</t>
+          <t>X &gt; 57.81</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1774</v>
+        <v>1780</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.313350411286898</v>
+        <v>1.336042021266863</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.276082249645206</v>
+        <v>1.243789741642551</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4316200273409905</v>
+        <v>0.4567933263615558</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.8429019443975889</v>
+        <v>0.8675762439807357</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5606301361327013</v>
+        <v>0.6030462041524132</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8329369558938353</v>
+        <v>0.8196519476904456</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.605289061456034</v>
+        <v>2.612928442734642</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.038614340010319</v>
+        <v>3.045972086845687</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.460846123370018</v>
+        <v>3.458437679956077</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>3.926743930601774</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.430658154316795</v>
+        <v>3.385524831380287</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.634145664056568</v>
+        <v>3.612230894587874</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.988515667563902</v>
+        <v>2.992353866900459</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.326990889380063</v>
+        <v>3.353758279477617</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.55</t>
+          <t>X &gt; 60.52</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1571</v>
+        <v>1576</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.267495659427532</v>
+        <v>1.262874858689422</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.562281612107036</v>
+        <v>1.490467435134825</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5957186136289891</v>
+        <v>0.5891152336221595</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.10713816636602</v>
+        <v>1.099709934735316</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.9855452353498748</v>
+        <v>0.9277196770321225</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.537210428367032</v>
+        <v>1.454312302450028</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.296111003620886</v>
+        <v>3.297209512716961</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.909779804207957</v>
+        <v>3.910056955379304</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.331659685023276</v>
+        <v>4.317246782790733</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.665408606537355</v>
+        <v>4.635550181671178</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.269746277048647</v>
+        <v>4.241054404185853</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.495085600632486</v>
+        <v>4.48957647149998</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.011281023576238</v>
+        <v>4.030966768286405</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.555285292516963</v>
+        <v>4.597270513550512</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 63.27</t>
+          <t>X &gt; 63.24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.071004310859671</v>
+        <v>2.003036718112305</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.668922058478628</v>
+        <v>1.699177330184597</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.487521939726442</v>
+        <v>1.447585752673014</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.759994593983365</v>
+        <v>1.71961620469083</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.688691975377878</v>
+        <v>1.656806296148289</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.341937891133973</v>
+        <v>2.284957841975043</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.178935716921174</v>
+        <v>4.143278298591788</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.637133977049025</v>
+        <v>4.601397208428772</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.259760422284316</v>
+        <v>5.204083447906051</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.593355585662295</v>
+        <v>5.517426153516091</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.103551077437736</v>
+        <v>5.028992884373743</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.423032579757425</v>
+        <v>5.371452443344893</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.789054213970743</v>
+        <v>4.76307490057637</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.513720726634908</v>
+        <v>5.509632200402677</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 65.98</t>
+          <t>X &gt; 65.95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.619485575891346</v>
+        <v>2.582109506307887</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.534403900498212</v>
+        <v>2.602781659323639</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.97898994546204</v>
+        <v>2.048658747191773</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.028893803909838</v>
+        <v>2.098350326497879</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.213495817079206</v>
+        <v>2.330833342723182</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.510869846714293</v>
+        <v>2.60361886154211</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.273549045681058</v>
+        <v>4.307196934305423</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.011299679002747</v>
+        <v>5.044251102550788</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.722150836443227</v>
+        <v>5.809203112499794</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.967109333664645</v>
+        <v>6.027876536496365</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.762408175404452</v>
+        <v>5.823736088960274</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.957687373616572</v>
+        <v>6.042287750142329</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.376635474446367</v>
+        <v>5.486744899761341</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.763272170529696</v>
+        <v>5.89617468559387</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 68.7</t>
+          <t>X &gt; 68.67</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.2672591519474</v>
+        <v>3.278402304556948</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.024686197569707</v>
+        <v>3.06259076178943</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.538673936902256</v>
+        <v>2.577695070648844</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.39517645275339</v>
+        <v>2.43410600338585</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.769295658781779</v>
+        <v>2.85643389069282</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.427983557030011</v>
+        <v>2.491115489730532</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.259331591924422</v>
+        <v>4.344771159848733</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.069635210911407</v>
+        <v>5.155146239027829</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.976889564070994</v>
+        <v>6.029750658149929</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.645423431920186</v>
+        <v>6.664445322549163</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.440722273659993</v>
+        <v>6.460304875013072</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.206361851975089</v>
+        <v>7.247733234985077</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.603395642171733</v>
+        <v>6.670259902769473</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.646315935908326</v>
+        <v>6.736989359133062</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 71.42</t>
+          <t>X &gt; 71.38</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.923820245030775</v>
+        <v>3.867165774255568</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.573129308048756</v>
+        <v>4.749154819860699</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.824213682174225</v>
+        <v>4.89132251214621</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.662727308001557</v>
+        <v>3.842214056040412</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.093221393226642</v>
+        <v>4.317595140168883</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.067667543421472</v>
+        <v>4.16165611450765</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.028167087276941</v>
+        <v>6.030260475442951</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.391023093651661</v>
+        <v>7.600869301340417</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.367261159095406</v>
+        <v>8.528526917284012</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.664675249720119</v>
+        <v>8.776509697669468</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.783598686929196</v>
+        <v>8.893912658493505</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.680975760535866</v>
+        <v>9.809528484818735</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.289951120814692</v>
+        <v>8.44974033317451</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.192062175571955</v>
+        <v>8.377241786829764</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 74.14</t>
+          <t>X &gt; 74.1</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.789492132730956</v>
+        <v>4.687340404412375</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.729326447830388</v>
+        <v>5.651934019893467</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.354963226340658</v>
+        <v>6.277304311833539</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.592331227071881</v>
+        <v>5.515468607825291</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.181592694384342</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.478966724019429</v>
+        <v>5.426393520724147</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.307521670875715</v>
+        <v>7.276565456976392</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.626167312803261</v>
+        <v>8.594172187038907</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.029777123335506</v>
+        <v>8.939365182997655</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.9244108873268</v>
+        <v>9.771587557596689</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.59183249121493</v>
+        <v>9.440058575028743</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.39347407068023</v>
+        <v>10.26255652258472</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.566673600998541</v>
+        <v>8.466124710670577</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.66453201337341</v>
+        <v>8.587781037654089</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 76.86</t>
+          <t>X &gt; 76.81</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.595289257179495</v>
+        <v>4.610631209168751</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.850355108128106</v>
+        <v>4.885039263331777</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.922146709376172</v>
+        <v>4.95569755984679</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.7413298622958</v>
+        <v>4.775984077841663</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.580956327862616</v>
+        <v>3.667539890450108</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.344893343500821</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.126434928247093</v>
+        <v>6.046851982582282</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.836660219141535</v>
+        <v>7.748201884737639</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.553283039290612</v>
+        <v>8.485223083650375</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.983369863034099</v>
+        <v>9.828577165374099</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.311378985147741</v>
+        <v>9.160040433008277</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>10.90338953625696</v>
+        <v>10.76619478647223</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.392896003815821</v>
+        <v>9.287445528639076</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.462868414166969</v>
+        <v>9.381691629044532</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 79.57</t>
+          <t>X &gt; 79.53</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.288314738696421</v>
+        <v>3.57353836522708</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.830974799478739</v>
+        <v>2.750817553835496</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.397741876262167</v>
+        <v>3.497763976167178</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.335659327542828</v>
+        <v>3.057305812058665</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.412754389831754</v>
+        <v>2.377942602665669</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.671666881005308</v>
+        <v>3.221070326807791</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.251668990434041</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.735272493337014</v>
+        <v>7.44743318822561</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.058905721429618</v>
+        <v>7.790688715970944</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.09360230971514</v>
+        <v>9.818571161771928</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>9.696593459147266</v>
+        <v>9.424316645794775</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.8463562268872</v>
+        <v>11.76385220445244</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.27235921972763</v>
+        <v>10.22800986724223</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.30578717764647</v>
+        <v>10.28694066081653</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 82.29</t>
+          <t>X &gt; 82.25</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>396</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.812013262394942</v>
+        <v>1.78281746804231</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.473554442058379</v>
+        <v>2.472367655613724</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.088884067404358</v>
+        <v>3.088730677400036</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.956482948366457</v>
+        <v>1.955988455988454</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.923243900321268</v>
+        <v>1.971789820087039</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.725668435006853</v>
+        <v>2.749625843956466</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.661160095942705</v>
+        <v>4.709171774933026</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.224394482458997</v>
+        <v>7.273642044852714</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.405836568360463</v>
+        <v>6.47909367814016</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.10137231748516</v>
+        <v>10.20071964277973</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.644145906699706</v>
+        <v>9.744053942718381</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.70882708935806</v>
+        <v>12.8325237103863</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.78362573099415</v>
+        <v>11.93231527877197</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.989159361018658</v>
+        <v>10.16115812058532</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 85.01</t>
+          <t>X &gt; 84.96</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.809186358544146</v>
+        <v>2.557455742680581</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.221891050463256</v>
+        <v>1.987792171038251</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.874901235674088</v>
+        <v>3.958919047588402</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.687720235917737</v>
+        <v>4.76447876447876</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.808133754494392</v>
+        <v>3.937391785689002</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.44680471245713</v>
+        <v>4.548015142345768</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.385985138173901</v>
+        <v>5.500872566633817</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.284104207697737</v>
+        <v>6.386391157601835</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.223122051174961</v>
+        <v>6.349418548465039</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.127469466449199</v>
+        <v>9.579644021704098</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.581471379861355</v>
+        <v>9.037665736330169</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.05270960047607</v>
+        <v>13.48772436558696</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.63255874716266</v>
+        <v>13.09256643902314</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.4931066840786</v>
+        <v>11.99025994968715</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 87.73</t>
+          <t>X &gt; 87.68</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.185750636132312</v>
+        <v>4.766883480277343</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.003135971639921</v>
+        <v>4.592157099346835</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.036936015456305</v>
+        <v>5.606869815257483</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.024304016187521</v>
+        <v>8.553655264922867</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.962204939282302</v>
+        <v>8.064406123970947</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>9.74564234701522</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.03201146679407</v>
+        <v>11.09343696201512</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.99351425157877</v>
+        <v>12.03605490585714</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>15.84451806063089</v>
+        <v>15.87008939665652</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>16.11600737856118</v>
+        <v>16.13543251719555</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>20.43609981663079</v>
+        <v>20.41895136723651</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>21.44452039188882</v>
+        <v>21.43224414489803</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>20.7178750897344</v>
+        <v>20.74232187076316</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 90.44</t>
+          <t>X &gt; 90.39</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.185750636132312</v>
+        <v>2.095151333007749</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.574564543068483</v>
+        <v>2.485658458378211</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.179793158313444</v>
+        <v>4.065604680589828</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.643351635235142</v>
+        <v>9.458646616541351</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.771728748806105</v>
+        <v>9.627292212431534</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.06910277844119</v>
+        <v>9.900077731250462</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.65105908584171</v>
+        <v>14.44468479991974</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>14.18399044205497</v>
+        <v>13.9788520395364</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.78967495219885</v>
+        <v>13.9418794303996</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.60642282253566</v>
+        <v>17.72331400747935</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.7350549976088</v>
+        <v>16.86127882310116</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>22.43609981663078</v>
+        <v>21.52470871836079</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>24.01594896331737</v>
+        <v>23.10323500232328</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>22.90835128021057</v>
+        <v>22.03649039065444</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 93.16</t>
+          <t>X &gt; 93.11</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5.852417302798983</v>
+        <v>5.823221508446352</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.227412205932488</v>
+        <v>6.227258815928167</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>11.11954211142562</v>
+        <v>11.11904761904762</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>11.7717287488061</v>
+        <v>11.82027466857188</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>14.45005515939359</v>
+        <v>14.4740125683432</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20.31772575250837</v>
+        <v>20.36573743149869</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>18.66018091824544</v>
+        <v>18.70942848063915</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>18.59919876172266</v>
+        <v>18.67245587150236</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18.93975615586899</v>
+        <v>19.03910348116356</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>19.92553118808499</v>
+        <v>20.02543922410366</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>23.5313379118689</v>
+        <v>23.65503453289714</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>24.30166324903166</v>
+        <v>24.45035279680949</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>23.33692270878202</v>
+        <v>23.50892146834868</v>
       </c>
     </row>
   </sheetData>
@@ -3904,209 +3904,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 14.35</t>
+          <t>X &lt; 14.36</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.290439840058163</v>
+        <v>-1.319635634410794</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.036936015456305</v>
+        <v>5.036782625451984</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.7852197933362888</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.438395415472783</v>
+        <v>3.486941335238555</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.026135316796896</v>
+        <v>-1.002177907847283</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.491798057015444</v>
+        <v>-3.443786378025123</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4.019848857324959</v>
+        <v>-3.946591747545263</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.679291463178622</v>
+        <v>-3.579944137884048</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>-0.3006023411751357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 17.07</t>
+          <t>X &lt; 17.08</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>134</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.235501879913407</v>
+        <v>4.206306085560776</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.878047130133154</v>
+        <v>1.876860343688499</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.214619028960207</v>
+        <v>5.214465638955886</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.106038202399318</v>
+        <v>3.105543710021315</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.552823276169292</v>
+        <v>5.601369195935064</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.865122678938711</v>
+        <v>2.889080087888324</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.526680976388967</v>
+        <v>3.574692655379287</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.059612332602228</v>
+        <v>3.108859894995945</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.717787734368308</v>
+        <v>-3.644530624588612</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.075169217265341</v>
+        <v>-2.975821891970767</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.752954909737369</v>
+        <v>-1.629258288709124</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.173105763050778</v>
+        <v>-2.02441621527295</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.947370112824245</v>
+        <v>-2.521640009974</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 19.78</t>
+          <t>X &lt; 19.79</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.934925553624062</v>
+        <v>6.02647354096667</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.323739460560233</v>
+        <v>4.443296455810817</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.384413620359652</v>
+        <v>7.95199749188636</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.01958925899752</v>
+        <v>8.569686411149824</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.471398715802813</v>
+        <v>8.568242148246682</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.798475715734931</v>
+        <v>6.210707246214341</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.713765356468762</v>
+        <v>6.15005115698888</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.751647207731523</v>
+        <v>5.194022318174163</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2352195066543032</v>
+        <v>0.7452850031550184</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.109748794626057</v>
+        <v>-0.5687396560913314</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.779796487539713</v>
+        <v>-4.440899035338042</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2899727906299319</v>
+        <v>0.05076523897265872</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.205173148893834</v>
+        <v>-0.8370035250295871</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.979437498667302</v>
+        <v>-1.080569500452647</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 22.5</t>
+          <t>X &lt; 22.51</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>283</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.996115771585785</v>
+        <v>3.279361859323537</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.151714130818775</v>
+        <v>3.450570739079971</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.463656526982469</v>
+        <v>3.407709943747726</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.947238561030197</v>
+        <v>4.239348370927317</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.882447241150047</v>
+        <v>5.85536238787013</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.119750599407048</v>
+        <v>5.285548450301611</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.681683349681514</v>
+        <v>4.872779685019815</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.507900924976042</v>
+        <v>3.702721572523792</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2667067543189887</v>
+        <v>0.4967348788799626</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.349996494307682</v>
+        <v>-2.087657082216722</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.674838995324066</v>
+        <v>-4.574930959305391</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.520319500212551</v>
+        <v>-2.396622879184306</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.000541024904059</v>
+        <v>-3.851851477126232</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.774805374677527</v>
+        <v>-3.956163505570224</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>373</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3.819352065980397</v>
+        <v>3.872866898517266</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.208165972916568</v>
+        <v>2.289689813361413</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.958166706123983</v>
+        <v>4.023611399514799</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.356488364457654</v>
+        <v>4.419452887537986</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.962970929324428</v>
+        <v>5.79190587424565</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.456055414723593</v>
+        <v>5.693060187390813</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.567055511221497</v>
+        <v>4.832404098165355</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.759504293708225</v>
+        <v>3.033238004448684</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5537500192229814</v>
+        <v>0.8629320619785545</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.904747865578727</v>
+        <v>-1.682821652526279</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.44993159756546</v>
+        <v>-3.350023561546784</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.611263900974215</v>
+        <v>-2.487567279945971</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.567607783778236</v>
+        <v>-3.418918236000408</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.073775618806401</v>
+        <v>-3.169873373985041</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.212961520486054</v>
+        <v>2.035342720567556</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.00993869272834</v>
+        <v>1.058226241472312</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.451902001850868</v>
+        <v>2.280649869319227</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.58212714543923</v>
+        <v>2.612554112554108</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.472409020914959</v>
+        <v>3.335426183723399</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.953456519937802</v>
+        <v>3.118701213031834</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.05241963005939</v>
+        <v>2.248328524616092</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.7690244556604071</v>
+        <v>1.175208314840042</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5164474967807422</v>
+        <v>-0.1674939015102908</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.99901935433509</v>
+        <v>-2.708863998511234</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.611883777901404</v>
+        <v>-3.415546131341969</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.373423992893017</v>
+        <v>-3.249727371864772</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.201738111512554</v>
+        <v>-4.053048563734727</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.459746879298621</v>
+        <v>-3.599922069066295</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.269486545955182</v>
+        <v>2.107722570017479</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.751698198463011</v>
+        <v>2.594609179129137</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.356926813707972</v>
+        <v>2.360106859604244</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.004060169856714</v>
+        <v>2.171519563239308</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.237107170706281</v>
+        <v>3.274627110185477</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.407267029648928</v>
+        <v>2.683171830134029</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.678434287129939</v>
+        <v>1.91525819827185</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.4062126642771844</v>
+        <v>0.7399046711153474</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.6209530671248231</v>
+        <v>-0.3293756303291389</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.309841267641474</v>
+        <v>-1.065230387215244</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.514542425901666</v>
+        <v>-1.341885840970598</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.641194869359552</v>
+        <v>-1.517498248331307</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.222376318486162</v>
+        <v>-2.073686770708335</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.74756269828405</v>
+        <v>-1.824641908692968</v>
       </c>
     </row>
     <row r="13">
@@ -4272,1193 +4272,1193 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8350787679051805</v>
+        <v>0.7717414569663035</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.82467290891158</v>
+        <v>1.762566945813013</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.039784489045999</v>
+        <v>1.11142870009806</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7798925975238262</v>
+        <v>0.9839124839124835</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.452266243387825</v>
+        <v>2.498968826647484</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.189172132580772</v>
+        <v>1.426393520724154</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.104461773314604</v>
+        <v>1.308889886279054</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4029189641002162</v>
+        <v>-0.11950024479669</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7239791440300252</v>
+        <v>-0.4738555027882896</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.573897940359885</v>
+        <v>-1.356486661508292</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.778599098620077</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.004298969671765</v>
+        <v>-1.880602348643521</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.684527846392193</v>
+        <v>-2.535838298614365</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.518732053122754</v>
+        <v>-2.546871460006031</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 36.09</t>
+          <t>X &lt; 36.08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.7379680896373202</v>
+        <v>0.6813775368151411</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.809185430049894</v>
+        <v>1.757774919744392</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.307117907955785</v>
+        <v>1.364036931429688</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.9008623648488765</v>
+        <v>1.068389057750764</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.401199421195244</v>
+        <v>2.448602677091593</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7672429787273245</v>
+        <v>0.9701035420461039</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5752364821221008</v>
+        <v>0.7552785200792584</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4283128483599228</v>
+        <v>-0.1855654143547341</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5965911422217545</v>
+        <v>-0.3777096492514005</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.339213801212559</v>
+        <v>-1.142909366802172</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.29498792084614</v>
+        <v>-2.145744361870911</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.831425219134594</v>
+        <v>-1.70772859810635</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.358872209787059</v>
+        <v>-2.210182662009231</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.289643707258094</v>
+        <v>-2.283026212011031</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 38.81</t>
+          <t>X &lt; 38.8</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1098</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2081887578070791</v>
+        <v>-0.1162545529809336</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.816988785492725</v>
+        <v>1.913937828891221</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.513126491646787</v>
+        <v>1.610534077252218</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.279715271598782</v>
+        <v>1.519891500904158</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.377789354866721</v>
+        <v>2.438675875208382</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.129708839047261</v>
+        <v>1.314074680144437</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.226816661599273</v>
+        <v>1.304087386167772</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.03247529053980003</v>
+        <v>0.253806667485577</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1194159568920554</v>
+        <v>0.0854570392719225</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5147892986764688</v>
+        <v>-0.3245328824727949</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.083126820573028</v>
+        <v>-0.9330078489930926</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2305668500358706</v>
+        <v>-0.09594126725900054</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.5087704785995086</v>
+        <v>-0.4000245125842028</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9605011788058206</v>
+        <v>-0.9706517817163842</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 41.53</t>
+          <t>X &lt; 41.51</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1422954162065082</v>
+        <v>0.133929216944118</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.755153246330224</v>
+        <v>1.707816062332853</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.519490851233094</v>
+        <v>1.55085786880899</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.251943520676669</v>
+        <v>1.330060934326333</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.668307905528465</v>
+        <v>1.675347132340001</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4541465334133576</v>
+        <v>0.5687985840152905</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5285451638051057</v>
+        <v>0.6309789200180873</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7340684282712147</v>
+        <v>-0.5834550753188807</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.033714069280862</v>
+        <v>-0.894403386078551</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.247196906979063</v>
+        <v>-1.119626677566586</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.24744301352883</v>
+        <v>-2.074488912361403</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.81529238702872</v>
+        <v>-1.655359895144358</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.555176302075402</v>
+        <v>-1.450317733932636</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.44490237184786</v>
+        <v>-1.439936356404147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 44.24</t>
+          <t>X &lt; 44.23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.04359012524187733</v>
+        <v>-0.0533644200426906</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.890476273614361</v>
+        <v>0.8548079757703064</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.262255411507404</v>
+        <v>1.291519814445223</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.253107732796124</v>
+        <v>1.321527502967946</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.202623057749207</v>
+        <v>1.217364065661286</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1759552755375964</v>
+        <v>0.2807624527629784</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.09124491627142817</v>
+        <v>0.1887769873626723</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7939421944142637</v>
+        <v>-0.6556508844402131</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.273042817835993</v>
+        <v>-1.141237500217429</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.844215969566541</v>
+        <v>-1.718893737195273</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.188289950126389</v>
+        <v>-2.024466333108784</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.362971031220546</v>
+        <v>-2.207148780539669</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.699532208230735</v>
+        <v>-1.589136169508741</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.854151627442363</v>
+        <v>-1.827896185542158</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 46.96</t>
+          <t>X &lt; 46.95</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1625</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.08533863495695471</v>
+        <v>-0.03304760470349777</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6712660386636458</v>
+        <v>0.7079343315473778</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5838087288932527</v>
+        <v>0.6811688202968895</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.205736392457027</v>
+        <v>1.334411610421405</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.220612174333667</v>
+        <v>1.246688222358372</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5960439790148584</v>
+        <v>0.6960013638614058</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6342592497425414</v>
+        <v>0.7305442984514769</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.5089003590103971</v>
+        <v>-0.3761689485165647</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7542709605239537</v>
+        <v>-0.6250974039514645</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.604189756853813</v>
+        <v>-1.476867034806951</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.931816545107857</v>
+        <v>-1.77044569409226</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.143289652740243</v>
+        <v>-1.98632902359558</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.23866358280808</v>
+        <v>-1.117412770956072</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.717289745430442</v>
+        <v>-1.606829447402248</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 49.68</t>
+          <t>X &lt; 49.66</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3573639069822363</v>
+        <v>-0.3696068852601968</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.04697072408394121</v>
+        <v>0.02306674308560019</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.03851280511256761</v>
+        <v>0.0983657430482765</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3092820604145956</v>
+        <v>0.3681318681318686</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.008135046518752631</v>
+        <v>0.0189186121306264</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.06836653695398809</v>
+        <v>0.1568665680288746</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2071361259446718</v>
+        <v>-0.1488470484132591</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.171442338792183</v>
+        <v>-1.080271540338408</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.840159301944794</v>
+        <v>-1.748638185955336</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.248089147998414</v>
+        <v>-2.157147897006233</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.508038925043138</v>
+        <v>-2.38676890239018</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.418412153903283</v>
+        <v>-2.298923209140078</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.592674585604669</v>
+        <v>-1.504789061148493</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.166132495600628</v>
+        <v>-2.139233983782482</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 52.4</t>
+          <t>X &lt; 52.38</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.833104913957861</v>
+        <v>-0.770768365798304</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.401157241708411</v>
+        <v>-0.3941218350795879</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.116770017003752</v>
+        <v>0.07179663105421952</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.07684917218094967</v>
+        <v>0.03226371470608314</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1789537077552126</v>
+        <v>0.1094470598051203</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3778055699026126</v>
+        <v>0.3601195884708375</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7640879488223433</v>
+        <v>-0.8032213111339317</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.37901267935132</v>
+        <v>-1.390021618810941</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.129989907337865</v>
+        <v>-2.138051222190583</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.388484356698775</v>
+        <v>-2.394738132215679</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.34675870372191</v>
+        <v>-2.32645428920717</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.236484009799184</v>
+        <v>-2.24177914087371</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.643317604681307</v>
+        <v>-1.62518086493106</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.229523020546246</v>
+        <v>-2.285511632639384</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 55.11</t>
+          <t>X &lt; 55.09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2218</v>
+        <v>2222</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.155073333905143</v>
+        <v>-1.122466345925474</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4500157926629242</v>
+        <v>-0.4675055617885846</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1240126814803446</v>
+        <v>0.103210450500498</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.171229822910675</v>
+        <v>-0.1904761904761969</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.01055263119435068</v>
+        <v>-0.02792494296255654</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.08290415857921118</v>
+        <v>0.09007065076898613</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.192855066942329</v>
+        <v>-1.157367099681217</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.479824656249107</v>
+        <v>-1.419664449171911</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.171153503451755</v>
+        <v>-2.106084552300757</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.435750372721735</v>
+        <v>-2.367006132493223</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.370302949261983</v>
+        <v>-2.277396516934324</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.401738021207045</v>
+        <v>-2.329891811741447</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.806193142736404</v>
+        <v>-1.75618919920619</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.051672765476219</v>
+        <v>-2.022560251251861</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 57.83</t>
+          <t>X &lt; 57.81</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2395</v>
+        <v>2400</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9619813655322744</v>
+        <v>-0.9761151416365692</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8031762285107575</v>
+        <v>-0.7765393246365377</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.259468260539812</v>
+        <v>-0.2771554757113392</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5233150314315225</v>
+        <v>-0.5397154712507444</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3116045845272239</v>
+        <v>-0.3424484530553471</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4725638882254657</v>
+        <v>-0.4623107982127337</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.743549778963079</v>
+        <v>-1.74685085267248</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.063437970511067</v>
+        <v>-2.066013865875512</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.332927216274875</v>
+        <v>-2.330415131368646</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.682428998426253</v>
+        <v>-2.674706834976206</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.303310306811547</v>
+        <v>-2.274067345065831</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.455014075734674</v>
+        <v>-2.443256573720376</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.97626027430087</v>
+        <v>-1.983077718253675</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.228739881932775</v>
+        <v>-2.252983293556092</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.55</t>
+          <t>X &lt; 60.52</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2598</v>
+        <v>2604</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7554559078349641</v>
+        <v>-0.7517020389542566</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.8124703629537606</v>
+        <v>-0.7676008366483416</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3042180977622806</v>
+        <v>-0.2996464012256084</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5754583455710005</v>
+        <v>-0.5698436987648989</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4995444437722583</v>
+        <v>-0.4644555266060664</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.7957205702531098</v>
+        <v>-0.7451225589083208</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.82019203466028</v>
+        <v>-1.819249163675572</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.190080785206128</v>
+        <v>-2.188217934248634</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.404790843343044</v>
+        <v>-2.396554331275574</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.601366057812797</v>
+        <v>-2.586663390002073</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.362599750564982</v>
+        <v>-2.348389478838961</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.499797619266651</v>
+        <v>-2.499809599690671</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.206700773760986</v>
+        <v>-2.221797829275872</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.537376202468401</v>
+        <v>-2.566347348855636</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 63.27</t>
+          <t>X &lt; 63.24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2766</v>
+        <v>2773</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.03999384033262</v>
+        <v>-1.002574136444778</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7227327542288151</v>
+        <v>-0.7360178148902321</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7017257073438472</v>
+        <v>-0.6795556339897288</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8045387362037317</v>
+        <v>-0.7818643806786127</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7658358623250336</v>
+        <v>-0.7486206106037727</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.062210352871929</v>
+        <v>-1.031715073306778</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.957626106026453</v>
+        <v>-1.936420841882601</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.189054082614113</v>
+        <v>-2.167385721112076</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.466642737331838</v>
+        <v>-2.437283920742836</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.63064095604436</v>
+        <v>-2.593953774868119</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.38267703561619</v>
+        <v>-2.346593162337946</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.54559575176998</v>
+        <v>-2.521284643422049</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.223540254849098</v>
+        <v>-2.212193981094167</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.592733318487909</v>
+        <v>-2.592687584937273</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 65.98</t>
+          <t>X &lt; 65.95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2926</v>
+        <v>2933</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.101957910003193</v>
+        <v>-1.084449910426699</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9585871372221604</v>
+        <v>-0.9863279592788317</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7901103056274934</v>
+        <v>-0.8185486374879716</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.7779162584253925</v>
+        <v>-0.8063443522159162</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.854706073332764</v>
+        <v>-0.903496008971743</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9481778036415633</v>
+        <v>-0.986391246361876</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.662826959876483</v>
+        <v>-1.675078895031923</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.975281457831279</v>
+        <v>-1.986791484039472</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.241041771350645</v>
+        <v>-2.277980123181429</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.340107325359675</v>
+        <v>-2.368795735724419</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.253336945033737</v>
+        <v>-2.282203178906585</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.337124227085063</v>
+        <v>-2.376035476026374</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.089733760745936</v>
+        <v>-2.139383302129062</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.255467357292268</v>
+        <v>-2.315035799522683</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 68.7</t>
+          <t>X &lt; 68.67</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3075</v>
+        <v>3083</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.152335343560928</v>
+        <v>-1.153522677600158</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9640632257051536</v>
+        <v>-0.9753567614160161</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8552262969394704</v>
+        <v>-0.8671173960950966</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7724771030068283</v>
+        <v>-0.7845596046372023</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9040229275944967</v>
+        <v>-0.9330672891685197</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.751410042071619</v>
+        <v>-0.7722476957106608</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.370585935803327</v>
+        <v>-1.398016613808764</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.657949581762296</v>
+        <v>-1.684750557113858</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.946278279369842</v>
+        <v>-1.963492808487771</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.179113607041039</v>
+        <v>-2.187006010252048</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.106400492969499</v>
+        <v>-2.114486091453536</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.379413128878902</v>
+        <v>-2.395362935652692</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.164371799578163</v>
+        <v>-2.189447092017637</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.181079614098358</v>
+        <v>-2.214708885511975</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 71.42</t>
+          <t>X &lt; 71.38</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3242</v>
+        <v>3247</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.112948001023128</v>
+        <v>-1.099068880101704</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.201573218309122</v>
+        <v>-1.254994954841862</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.333997470211116</v>
+        <v>-1.35627183390082</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9720329801494714</v>
+        <v>-1.025856397210411</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.093768327217283</v>
+        <v>-1.160888312591091</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.056923494136797</v>
+        <v>-1.086663314913331</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.587109480013957</v>
+        <v>-1.591853226153425</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.97620672368749</v>
+        <v>-2.041380296606761</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.222031763759247</v>
+        <v>-2.277289340235477</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.301771878635016</v>
+        <v>-2.346623987307673</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.335823276659305</v>
+        <v>-2.38042158175714</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.593082263106162</v>
+        <v>-2.644266350891293</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.194966855369017</v>
+        <v>-2.253259682665053</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.168350344301039</v>
+        <v>-2.233888744741797</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 74.14</t>
+          <t>X &lt; 74.1</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3387</v>
+        <v>3395</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.097749461964604</v>
+        <v>-1.072318397656936</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.22192255338917</v>
+        <v>-1.202182364695027</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.424447124372065</v>
+        <v>-1.404231830829652</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.219682238108007</v>
+        <v>-1.200020977554018</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.123576692168157</v>
+        <v>-1.115487180233444</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.164024247789278</v>
+        <v>-1.150156582126272</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.557274247491634</v>
+        <v>-1.547842815414889</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.861227291160418</v>
+        <v>-1.851050930178396</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.922209447683194</v>
+        <v>-1.901773820374395</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.123352071792461</v>
+        <v>-2.092111582090332</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.046655916845481</v>
+        <v>-2.015537260663287</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.232337283792148</v>
+        <v>-2.206369787441545</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.81010377182627</v>
+        <v>-1.790602949446608</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.833898498354529</v>
+        <v>-1.819993602834444</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 76.86</t>
+          <t>X &lt; 76.81</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3527</v>
+        <v>3534</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.8279067058663685</v>
+        <v>-0.8326379032630769</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7851490427615531</v>
+        <v>-0.793796524256031</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8538511730408089</v>
+        <v>-0.8622032030119868</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7932999484752656</v>
+        <v>-0.8018381167365405</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.580935089006239</v>
+        <v>-0.598579409892686</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6926402889045775</v>
+        <v>-0.6775025831719574</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9885295545960844</v>
+        <v>-0.9771035738670335</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.298833265004305</v>
+        <v>-1.28653600685076</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.40120581812117</v>
+        <v>-1.393072459072592</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.656392244017724</v>
+        <v>-1.636419413126987</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.534066815422364</v>
+        <v>-1.514202926225501</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.82421944283837</v>
+        <v>-1.808227695070983</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.548676887022765</v>
+        <v>-1.537388834496497</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.562492685388129</v>
+        <v>-1.555756355242565</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 79.57</t>
+          <t>X &lt; 79.53</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3649</v>
+        <v>3654</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4601623440242477</v>
+        <v>-0.5057485851815002</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3089827573048183</v>
+        <v>-0.301690437593308</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.4431576613586898</v>
+        <v>-0.4624702817136139</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4074819258471152</v>
+        <v>-0.3724266999376269</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2749269829234251</v>
+        <v>-0.2736374253402047</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.427479119289174</v>
+        <v>-0.3682542127548274</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6341342037279531</v>
+        <v>-0.6326236720249483</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9769762702113383</v>
+        <v>-0.9470898644037788</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9957656608279635</v>
+        <v>-0.9692625267068919</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.283348141968396</v>
+        <v>-1.258873555468476</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.226609843574117</v>
+        <v>-1.201952470884422</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.533223656390305</v>
+        <v>-1.539036530977</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.308251949924632</v>
+        <v>-1.317349632999644</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.313992740982442</v>
+        <v>-1.32687491917185</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 82.29</t>
+          <t>X &lt; 82.25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3773</v>
+        <v>3784</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1829762524044014</v>
+        <v>-0.1793243610997877</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1687203534528763</v>
+        <v>-0.1681045054063759</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2849707599388438</v>
+        <v>-0.2841283476329011</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1404178598745602</v>
+        <v>-0.1399578281497185</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1355513499070895</v>
+        <v>-0.1403545607101222</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1939669561969026</v>
+        <v>-0.1959693484741578</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.370104935322324</v>
+        <v>-0.3741728824026609</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.6375672892672597</v>
+        <v>-0.6409924265099889</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5253065194792867</v>
+        <v>-0.5316311473115007</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.9106542227383727</v>
+        <v>-0.9186578704731829</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.8624026295098446</v>
+        <v>-0.8706086590052209</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.184209234141839</v>
+        <v>-1.194033461971181</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.086329786020194</v>
+        <v>-1.099121946852833</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.8988755066080429</v>
+        <v>-0.9147169087780824</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 85.01</t>
+          <t>X &lt; 84.96</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3876</v>
+        <v>3884</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2052667633705596</v>
+        <v>-0.1878126203706856</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07975644458583986</v>
+        <v>-0.06351478273277422</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2548179385050062</v>
+        <v>-0.2636636120931044</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2907708557581685</v>
+        <v>-0.2996184606354078</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.223123246045887</v>
+        <v>-0.2355520289193436</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2463795421904464</v>
+        <v>-0.2570597166859301</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2913394032989913</v>
+        <v>-0.303756271919454</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3579982235813119</v>
+        <v>-0.3700182080620351</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3275628731039077</v>
+        <v>-0.3414906688005814</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.54477992660523</v>
+        <v>-0.585382115544256</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.5031507255157166</v>
+        <v>-0.5437351912245987</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.8411908830425858</v>
+        <v>-0.8829896319927073</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8085717141824063</v>
+        <v>-0.8520925056358166</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7232276671578433</v>
+        <v>-0.7689462183758664</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 87.73</t>
+          <t>X &lt; 87.68</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3959</v>
+        <v>3967</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2150550033440197</v>
+        <v>-0.2488052922236648</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1258467723012799</v>
+        <v>-0.1601398776226333</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2299465562121625</v>
+        <v>-0.2637991457180249</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.363199133220391</v>
+        <v>-0.3968712956643614</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3586475952799049</v>
+        <v>-0.3695308310927672</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.4256455620343971</v>
+        <v>-0.4352416994016366</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4714825177891697</v>
+        <v>-0.4822746470116286</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5213479354145605</v>
+        <v>-0.5317590590633614</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4676408903843949</v>
+        <v>-0.4794647154635499</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6981444244994179</v>
+        <v>-0.7103299109291115</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7121938666011971</v>
+        <v>-0.724230921032472</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.9414984329694747</v>
+        <v>-0.9544388861000925</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.9941520467836256</v>
+        <v>-1.008076542668235</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.9564293883084005</v>
+        <v>-0.9719144758096903</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 90.44</t>
+          <t>X &lt; 90.39</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4019</v>
+        <v>4028</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.07516206228038413</v>
+        <v>-0.07259635841828782</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.01122889114965631</v>
+        <v>-0.009130494201251338</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1196278507849797</v>
+        <v>-0.1171333603530869</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2985694369912153</v>
+        <v>-0.2957263142998698</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3020878682081189</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2891457109222557</v>
+        <v>-0.2871842790776356</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4348822951816445</v>
+        <v>-0.4335190740775232</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4164236366199887</v>
+        <v>-0.4149193249183725</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4141023837852487</v>
+        <v>-0.388741630062114</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5544024322493257</v>
+        <v>-0.5293488997888218</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5215337642012443</v>
+        <v>-0.4964683729713784</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6971174593370506</v>
+        <v>-0.6726270528289788</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.7551953152895834</v>
+        <v>-0.7313654601135298</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.7146063377706753</v>
+        <v>-0.6919108010039565</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 93.16</t>
+          <t>X &lt; 93.11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4085</v>
+        <v>4096</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1139077338042398</v>
+        <v>-0.1129348961938703</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.0206633145272761</v>
+        <v>0.02063514059007332</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.09234225835322007</v>
+        <v>-0.09209142234098522</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1686141767306708</v>
+        <v>-0.1681511377078877</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1807219921155578</v>
+        <v>-0.1813493671569049</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2120276067693183</v>
+        <v>-0.2120080387300405</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3078851956832338</v>
+        <v>-0.3081597169292891</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2727845925739061</v>
+        <v>-0.2731816282508177</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2469998644270675</v>
+        <v>-0.2480164871558088</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2519777644049128</v>
+        <v>-0.2535794456657001</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2717943174597011</v>
+        <v>-0.2733560685925767</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3460549831408386</v>
+        <v>-0.3479634452106666</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3609477571916813</v>
+        <v>-0.3633901277462215</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3417507189734224</v>
+        <v>-0.3447801685560918</v>
       </c>
     </row>
   </sheetData>
